--- a/reports/latest/android/Excel/Automation_Test_Report.xlsx
+++ b/reports/latest/android/Excel/Automation_Test_Report.xlsx
@@ -604,12 +604,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>21.98</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:00:13</t>
+          <t>2026-06-23 16:30:21</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -642,12 +642,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>26.31</t>
+          <t>25.37</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:00:31</t>
+          <t>2026-06-23 16:30:39</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -673,176 +673,24 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:01:17</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>TC_GEN_004</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>test_market_prices_page_load</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>35.58</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-23 16:01:49</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>TC_GEN_005</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>test_ai_advisor_page_load</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>31.83</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-23 16:02:23</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>TC_GEN_006</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>test_disease_scanner_page_load</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>33.46</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-23 16:02:56</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>TC_GEN_007</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>test_navigation_between_screens</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>29.99</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-23 16:03:31</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>driver = &lt;appium.webdriver.webdriver.WebDriver (session="5d941e00-69e0-4516-8ef1-9aad1eb798d1")&gt;
+          <t>2026-06-23 16:31:25</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>driver = &lt;appium.webdriver.webdriver.WebDriver (session="780dd579-ad7d-405b-92c8-18302ab263c6")&gt;
     @pytest.fixture(scope="function")
     def auth_driver(driver):
         """Fixture to launch app and log in automatically with test credentials."""
@@ -873,8 +721,8 @@
 /opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/selenium/webdriver/remote/webdriver.py:492: in execute
     self.error_handler.check_response(response)
 _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ 
-self = &lt;appium.webdriver.errorhandler.MobileErrorHandler object at 0x7f904310df50&gt;
-response = {'status': 500, 'value': '{"value":{"error":"unknown error","message":"Timed out after 10504ms waiting for the root Ac...r2.core.AccessibilityNodeInfoDumper.findNodesUsingXpath2(AccessibilityNodeInfoDumper.java:327)\\n\\t... 33 more\\n"}}'}
+self = &lt;appium.webdriver.errorhandler.MobileErrorHandler object at 0x7f052231b410&gt;
+response = {'status': 500, 'value': '{"value":{"error":"unknown error","message":"Timed out after 10510ms waiting for the root Ac...r2.core.AccessibilityNodeInfoDumper.findNodesUsingXpath2(AccessibilityNodeInfoDumper.java:327)\\n\\t... 33 more\\n"}}'}
     def check_response(self, response: Dict[str, Any]) -&gt; None:
         """
         https://www.w3.org/TR/webdriver/#errors
@@ -915,9 +763,9 @@
                 alert_text=value.get('data'),
             )
 &gt;       raise exception_class(msg=message, stacktrace=format_stacktrace(stacktrace))
-E       selenium.common.exceptions.WebDriverException: Message: Timed out after 10504ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work. Try changing the 'enforceXPath1' driver setting to 'true' in order to workaround the problem.
+E       selenium.common.exceptions.WebDriverException: Message: Timed out after 10510ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work. Try changing the 'enforceXPath1' driver setting to 'true' in order to workaround the problem.
 E       Stacktrace:
-E       io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: Timed out after 10504ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work. Try changing the 'enforceXPath1' driver setting to 'true' in order to workaround the problem.
+E       io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: Timed out after 10510ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work. Try changing the 'enforceXPath1' driver setting to 'true' in order to workaround the problem.
 E       	at io.appium.uiautomator2.core.AccessibilityNodeInfoDumper.findNodesUsingXpath2(AccessibilityNodeInfoDumper.java:366)
 E       	at io.appium.uiautomator2.core.AccessibilityNodeInfoDumper.findNodes(AccessibilityNodeInfoDumper.java:378)
 E       	at io.appium.uiautomator2.utils.ElementLocationHelpers.getXPathNodeMatch(ElementLocationHelpers.java:124)
@@ -952,7 +800,7 @@
 E       	at io.netty.util.internal.ThreadExecutorMap$2.run(ThreadExecutorMap.java:74)
 E       	at io.netty.util.concurrent.FastThreadLocalRunnable.run(FastThreadLocalRunnable.java:30)
 E       	at java.lang.Thread.run(Thread.java:919)
-E       Caused by: io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: Timed out after 10504ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work
+E       Caused by: io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: Timed out after 10510ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work
 E       	at io.appium.uiautomator2.utils.AXWindowHelpers.getActiveWindowRoot(AXWindowHelpers.java:107)
 E       	at io.appium.uiautomator2.utils.AXWindowHelpers.retrieveWindowRoots(AXWindowHelpers.java:87)
 E       	at io.appium.uiautomator2.utils.AXWindowHelpers.getCachedWindowRoots(AXWindowHelpers.java:68)
@@ -963,6 +811,158 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>TC_GEN_004</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>test_market_prices_page_load</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>34.83</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-23 16:31:54</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>TC_GEN_005</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>test_ai_advisor_page_load</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>32.37</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-23 16:32:27</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>TC_GEN_006</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>test_disease_scanner_page_load</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>32.02</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-23 16:33:00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>TC_GEN_007</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>test_navigation_between_screens</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>39.11</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-23 16:33:33</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr"/>
+    </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -991,12 +991,12 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>36.50</t>
+          <t>34.86</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:00</t>
+          <t>2026-06-23 16:34:11</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -5513,12 +5513,12 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -5860,7 +5860,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -5936,7 +5936,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -6658,7 +6658,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -7152,7 +7152,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -7228,7 +7228,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -7532,7 +7532,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -7646,7 +7646,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -7988,7 +7988,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -8140,7 +8140,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -8406,7 +8406,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -8444,7 +8444,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -8482,7 +8482,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -8710,7 +8710,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -8748,7 +8748,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -8824,7 +8824,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -9166,7 +9166,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -9280,7 +9280,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -9318,7 +9318,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -9432,7 +9432,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -9888,7 +9888,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -10040,7 +10040,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -10116,7 +10116,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -10306,7 +10306,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -10344,7 +10344,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -10420,7 +10420,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -10458,7 +10458,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -10496,7 +10496,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -10648,7 +10648,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -10686,7 +10686,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -10724,7 +10724,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -10762,7 +10762,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -10838,7 +10838,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -10876,7 +10876,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -10990,7 +10990,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -11256,7 +11256,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -11294,7 +11294,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -11408,7 +11408,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -11522,7 +11522,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -11712,7 +11712,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -11788,7 +11788,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -12016,7 +12016,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -12054,7 +12054,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -12206,7 +12206,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -12244,7 +12244,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -12282,7 +12282,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -12320,7 +12320,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -12358,7 +12358,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -12396,7 +12396,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -12434,7 +12434,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -12472,7 +12472,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -12586,7 +12586,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -12624,7 +12624,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -12662,7 +12662,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -12700,7 +12700,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -12738,7 +12738,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -12776,7 +12776,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -12814,7 +12814,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -12852,7 +12852,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -12928,7 +12928,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -12966,7 +12966,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -13004,7 +13004,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -13042,7 +13042,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -13080,7 +13080,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -13156,7 +13156,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -13270,7 +13270,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -13308,7 +13308,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -13346,7 +13346,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -13384,7 +13384,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -13422,7 +13422,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -13460,7 +13460,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -13536,7 +13536,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -13612,7 +13612,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -13650,7 +13650,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -13688,7 +13688,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -13726,7 +13726,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -13764,7 +13764,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -13802,7 +13802,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -13840,7 +13840,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -13954,7 +13954,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -13992,7 +13992,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -14030,7 +14030,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -14068,7 +14068,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -14144,7 +14144,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -14182,7 +14182,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -14220,7 +14220,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -14258,7 +14258,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -14334,7 +14334,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -14410,7 +14410,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -14524,7 +14524,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -14562,7 +14562,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -14600,7 +14600,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -14638,7 +14638,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -14676,7 +14676,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -14752,7 +14752,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -14790,7 +14790,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -14828,7 +14828,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -14904,7 +14904,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -14942,7 +14942,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -14980,7 +14980,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -15018,7 +15018,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -15056,7 +15056,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -15094,7 +15094,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -15132,7 +15132,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -15170,7 +15170,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -15208,7 +15208,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -15246,7 +15246,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -15322,7 +15322,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -15436,7 +15436,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -15512,7 +15512,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -15550,7 +15550,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -15588,7 +15588,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -15626,7 +15626,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -15740,7 +15740,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -15778,7 +15778,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -15816,7 +15816,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -15892,7 +15892,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -15930,7 +15930,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -15968,7 +15968,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -16120,7 +16120,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -16158,7 +16158,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -16196,7 +16196,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -16234,7 +16234,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -16272,7 +16272,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -16348,7 +16348,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -16386,7 +16386,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -16462,7 +16462,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -16538,7 +16538,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -16614,7 +16614,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -16690,7 +16690,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -16728,7 +16728,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -16766,7 +16766,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -16804,7 +16804,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -16842,7 +16842,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -16880,7 +16880,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -16956,7 +16956,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -16994,7 +16994,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -17032,7 +17032,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -17070,7 +17070,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -17108,7 +17108,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -17146,7 +17146,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -17222,7 +17222,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -17260,7 +17260,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -17298,7 +17298,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -17374,7 +17374,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -17450,7 +17450,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -17488,7 +17488,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -17526,7 +17526,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -17564,7 +17564,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -17602,7 +17602,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -17678,7 +17678,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -17716,7 +17716,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -17754,7 +17754,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -17792,7 +17792,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -17830,7 +17830,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -17868,7 +17868,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -17944,7 +17944,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -17982,7 +17982,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -18020,7 +18020,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -18058,7 +18058,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -18096,7 +18096,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -18172,7 +18172,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -18210,7 +18210,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -18248,7 +18248,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -18324,7 +18324,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -18362,7 +18362,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -18400,7 +18400,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -18438,7 +18438,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -18476,7 +18476,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -18552,7 +18552,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -18628,7 +18628,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -18666,7 +18666,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -18704,7 +18704,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -18742,7 +18742,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -18780,7 +18780,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -18818,7 +18818,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H480" s="4" t="inlineStr"/>
@@ -18856,7 +18856,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H481" s="4" t="inlineStr"/>
@@ -18894,7 +18894,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H482" s="4" t="inlineStr"/>
@@ -18932,7 +18932,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H483" s="4" t="inlineStr"/>
@@ -18970,7 +18970,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H484" s="4" t="inlineStr"/>
@@ -19008,7 +19008,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H485" s="4" t="inlineStr"/>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H486" s="4" t="inlineStr"/>
@@ -19084,7 +19084,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H487" s="4" t="inlineStr"/>
@@ -19122,7 +19122,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H488" s="4" t="inlineStr"/>
@@ -19160,7 +19160,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H489" s="4" t="inlineStr"/>
@@ -19198,7 +19198,7 @@
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H490" s="4" t="inlineStr"/>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H491" s="4" t="inlineStr"/>
@@ -19274,7 +19274,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H492" s="4" t="inlineStr"/>
@@ -19312,7 +19312,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H493" s="4" t="inlineStr"/>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H494" s="4" t="inlineStr"/>
@@ -19388,7 +19388,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H495" s="4" t="inlineStr"/>
@@ -19426,7 +19426,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H496" s="4" t="inlineStr"/>
@@ -19464,7 +19464,7 @@
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H497" s="4" t="inlineStr"/>
@@ -19502,7 +19502,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H498" s="4" t="inlineStr"/>
@@ -19540,7 +19540,7 @@
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H499" s="4" t="inlineStr"/>
@@ -19578,7 +19578,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H500" s="4" t="inlineStr"/>
@@ -19616,7 +19616,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H501" s="4" t="inlineStr"/>
@@ -19654,7 +19654,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H502" s="4" t="inlineStr"/>
@@ -19692,7 +19692,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H503" s="4" t="inlineStr"/>
@@ -19730,7 +19730,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H504" s="4" t="inlineStr"/>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H505" s="4" t="inlineStr"/>
@@ -19806,7 +19806,7 @@
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H506" s="4" t="inlineStr"/>
@@ -19844,7 +19844,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H507" s="4" t="inlineStr"/>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H508" s="4" t="inlineStr"/>
@@ -19920,7 +19920,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H509" s="4" t="inlineStr"/>
@@ -19958,7 +19958,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H510" s="4" t="inlineStr"/>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H511" s="4" t="inlineStr"/>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H512" s="4" t="inlineStr"/>
@@ -20072,7 +20072,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H513" s="4" t="inlineStr"/>
@@ -20110,7 +20110,7 @@
       </c>
       <c r="G514" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H514" s="4" t="inlineStr"/>
@@ -20148,7 +20148,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H515" s="4" t="inlineStr"/>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H516" s="4" t="inlineStr"/>
@@ -20224,7 +20224,7 @@
       </c>
       <c r="G517" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H517" s="4" t="inlineStr"/>
@@ -20262,7 +20262,7 @@
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H518" s="4" t="inlineStr"/>
@@ -20300,7 +20300,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H519" s="4" t="inlineStr"/>
@@ -20338,7 +20338,7 @@
       </c>
       <c r="G520" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H520" s="4" t="inlineStr"/>
@@ -20376,7 +20376,7 @@
       </c>
       <c r="G521" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H521" s="4" t="inlineStr"/>
@@ -20481,12 +20481,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>21.98</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:00:13</t>
+          <t>2026-06-23 16:30:21</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -20519,12 +20519,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>26.31</t>
+          <t>25.37</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:00:31</t>
+          <t>2026-06-23 16:30:39</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -20532,7 +20532,7 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>TC_GEN_003</t>
+          <t>TC_GEN_004</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -20542,7 +20542,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>test_home_page_load</t>
+          <t>test_market_prices_page_load</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -20557,12 +20557,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>34.83</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:01:17</t>
+          <t>2026-06-23 16:31:54</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -20570,7 +20570,7 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>TC_GEN_004</t>
+          <t>TC_GEN_005</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -20580,7 +20580,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>test_market_prices_page_load</t>
+          <t>test_ai_advisor_page_load</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -20595,12 +20595,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>35.58</t>
+          <t>32.37</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:01:49</t>
+          <t>2026-06-23 16:32:27</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -20608,7 +20608,7 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>TC_GEN_005</t>
+          <t>TC_GEN_006</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -20618,7 +20618,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>test_ai_advisor_page_load</t>
+          <t>test_disease_scanner_page_load</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -20633,12 +20633,12 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>32.02</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:02:23</t>
+          <t>2026-06-23 16:33:00</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -20646,7 +20646,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>TC_GEN_006</t>
+          <t>TC_GEN_007</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -20656,7 +20656,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>test_disease_scanner_page_load</t>
+          <t>test_navigation_between_screens</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -20671,12 +20671,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>33.46</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:02:56</t>
+          <t>2026-06-23 16:33:33</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -20709,12 +20709,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>36.50</t>
+          <t>34.86</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:00</t>
+          <t>2026-06-23 16:34:11</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -20752,7 +20752,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -20790,7 +20790,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -20828,7 +20828,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -20866,7 +20866,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -20904,7 +20904,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -20942,7 +20942,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -20980,7 +20980,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -21018,7 +21018,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -21056,7 +21056,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -21094,7 +21094,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -21132,7 +21132,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -21170,7 +21170,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -21208,7 +21208,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -21246,7 +21246,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -21284,7 +21284,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -21322,7 +21322,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -21360,7 +21360,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -21398,7 +21398,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -21436,7 +21436,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -21474,7 +21474,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -21512,7 +21512,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -21550,7 +21550,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -21588,7 +21588,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -21626,7 +21626,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -21664,7 +21664,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -21702,7 +21702,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -21740,7 +21740,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -21778,7 +21778,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -21816,7 +21816,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -21892,7 +21892,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -21930,7 +21930,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -21968,7 +21968,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -22006,7 +22006,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -22044,7 +22044,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -22082,7 +22082,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -22120,7 +22120,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -22158,7 +22158,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -22196,7 +22196,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -22234,7 +22234,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -22272,7 +22272,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -22310,7 +22310,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -22348,7 +22348,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -22386,7 +22386,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -22424,7 +22424,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -22462,7 +22462,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -22500,7 +22500,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -22538,7 +22538,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -22576,7 +22576,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -22614,7 +22614,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -22652,7 +22652,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -22690,7 +22690,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -22728,7 +22728,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -22766,7 +22766,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -22804,7 +22804,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -22842,7 +22842,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -22880,7 +22880,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -22918,7 +22918,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -22956,7 +22956,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -23032,7 +23032,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -23108,7 +23108,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -23146,7 +23146,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -23184,7 +23184,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -23222,7 +23222,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -23260,7 +23260,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -23298,7 +23298,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -23336,7 +23336,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -23374,7 +23374,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -23412,7 +23412,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -23450,7 +23450,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -23488,7 +23488,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -23526,7 +23526,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -23564,7 +23564,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -23602,7 +23602,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -23640,7 +23640,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -23678,7 +23678,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -23716,7 +23716,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -23754,7 +23754,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -23792,7 +23792,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -23830,7 +23830,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -23868,7 +23868,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -23906,7 +23906,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -23944,7 +23944,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -23982,7 +23982,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -24020,7 +24020,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -24058,7 +24058,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -24096,7 +24096,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -24134,7 +24134,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -24172,7 +24172,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -24210,7 +24210,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -24248,7 +24248,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -24286,7 +24286,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -24324,7 +24324,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -24362,7 +24362,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -24400,7 +24400,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -24438,7 +24438,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -24476,7 +24476,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -24514,7 +24514,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -24552,7 +24552,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -24628,7 +24628,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -24666,7 +24666,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -24704,7 +24704,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -24742,7 +24742,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -24780,7 +24780,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -24818,7 +24818,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -24856,7 +24856,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -24894,7 +24894,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -24932,7 +24932,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -24970,7 +24970,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -25008,7 +25008,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -25046,7 +25046,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -25084,7 +25084,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -25160,7 +25160,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -25198,7 +25198,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -25231,12 +25231,12 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -25312,7 +25312,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -25350,7 +25350,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -25388,7 +25388,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -25426,7 +25426,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -25464,7 +25464,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -25502,7 +25502,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -25540,7 +25540,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -25578,7 +25578,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -25616,7 +25616,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -25692,7 +25692,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -25768,7 +25768,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -25806,7 +25806,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -25844,7 +25844,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -25882,7 +25882,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -25920,7 +25920,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -25958,7 +25958,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -25996,7 +25996,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -26034,7 +26034,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -26072,7 +26072,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -26110,7 +26110,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -26148,7 +26148,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -26186,7 +26186,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -26224,7 +26224,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -26262,7 +26262,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -26300,7 +26300,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -26338,7 +26338,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -26376,7 +26376,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -26414,7 +26414,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -26452,7 +26452,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -26490,7 +26490,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -26528,7 +26528,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -26566,7 +26566,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -26642,7 +26642,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -26680,7 +26680,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -26718,7 +26718,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -26756,7 +26756,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -26794,7 +26794,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -26832,7 +26832,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -26870,7 +26870,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -26908,7 +26908,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -26946,7 +26946,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -26984,7 +26984,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -27022,7 +27022,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -27060,7 +27060,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -27098,7 +27098,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -27136,7 +27136,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -27174,7 +27174,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -27212,7 +27212,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -27250,7 +27250,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -27288,7 +27288,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -27326,7 +27326,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -27364,7 +27364,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -27402,7 +27402,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -27440,7 +27440,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -27516,7 +27516,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -27554,7 +27554,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -27592,7 +27592,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -27630,7 +27630,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -27668,7 +27668,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -27706,7 +27706,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -27744,7 +27744,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -27782,7 +27782,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -27820,7 +27820,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -27858,7 +27858,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -27896,7 +27896,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -27934,7 +27934,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -27972,7 +27972,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -28010,7 +28010,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -28048,7 +28048,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -28086,7 +28086,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -28124,7 +28124,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -28162,7 +28162,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -28200,7 +28200,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -28238,7 +28238,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -28276,7 +28276,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -28352,7 +28352,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -28390,7 +28390,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -28428,7 +28428,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -28466,7 +28466,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -28504,7 +28504,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -28542,7 +28542,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -28580,7 +28580,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -28618,7 +28618,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -28656,7 +28656,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -28694,7 +28694,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -28732,7 +28732,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -28770,7 +28770,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -28808,7 +28808,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -28846,7 +28846,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -28884,7 +28884,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -28922,7 +28922,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -28960,7 +28960,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -28998,7 +28998,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -29036,7 +29036,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -29074,7 +29074,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -29112,7 +29112,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -29150,7 +29150,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -29188,7 +29188,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -29264,7 +29264,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -29302,7 +29302,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -29340,7 +29340,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -29378,7 +29378,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -29416,7 +29416,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -29454,7 +29454,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -29492,7 +29492,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -29530,7 +29530,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -29568,7 +29568,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -29606,7 +29606,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -29644,7 +29644,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -29682,7 +29682,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -29720,7 +29720,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -29758,7 +29758,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -29796,7 +29796,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -29834,7 +29834,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -29872,7 +29872,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -29910,7 +29910,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -29948,7 +29948,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -29986,7 +29986,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -30024,7 +30024,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -30062,7 +30062,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -30138,7 +30138,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -30176,7 +30176,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -30214,7 +30214,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -30252,7 +30252,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -30290,7 +30290,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -30328,7 +30328,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -30366,7 +30366,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -30404,7 +30404,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -30442,7 +30442,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -30480,7 +30480,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -30518,7 +30518,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -30556,7 +30556,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -30594,7 +30594,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -30632,7 +30632,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -30670,7 +30670,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -30708,7 +30708,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -30746,7 +30746,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -30784,7 +30784,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -30822,7 +30822,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -30860,7 +30860,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -30898,7 +30898,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -30936,7 +30936,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -31012,7 +31012,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -31050,7 +31050,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -31088,7 +31088,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -31126,7 +31126,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -31164,7 +31164,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -31202,7 +31202,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -31240,7 +31240,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -31278,7 +31278,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -31316,7 +31316,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -31354,7 +31354,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -31392,7 +31392,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -31430,7 +31430,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -31468,7 +31468,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -31506,7 +31506,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -31544,7 +31544,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -31582,7 +31582,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -31620,7 +31620,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -31658,7 +31658,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -31696,7 +31696,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -31734,7 +31734,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -31772,7 +31772,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -31810,7 +31810,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -31886,7 +31886,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -31924,7 +31924,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -31962,7 +31962,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -32000,7 +32000,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -32038,7 +32038,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -32114,7 +32114,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -32152,7 +32152,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -32190,7 +32190,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -32266,7 +32266,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -32304,7 +32304,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -32342,7 +32342,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -32380,7 +32380,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -32418,7 +32418,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -32456,7 +32456,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -32494,7 +32494,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -32532,7 +32532,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -32570,7 +32570,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -32608,7 +32608,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -32646,7 +32646,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -32684,7 +32684,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -32760,7 +32760,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -32798,7 +32798,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -32836,7 +32836,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -32874,7 +32874,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -32912,7 +32912,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -32950,7 +32950,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -32988,7 +32988,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -33026,7 +33026,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -33064,7 +33064,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -33102,7 +33102,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -33140,7 +33140,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -33178,7 +33178,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -33216,7 +33216,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -33254,7 +33254,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -33292,7 +33292,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -33330,7 +33330,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -33368,7 +33368,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -33406,7 +33406,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -33444,7 +33444,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -33482,7 +33482,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -33520,7 +33520,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -33558,7 +33558,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -33634,7 +33634,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -33672,7 +33672,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -33710,7 +33710,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -33748,7 +33748,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -33786,7 +33786,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -33824,7 +33824,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -33862,7 +33862,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -33900,7 +33900,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -33938,7 +33938,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -33976,7 +33976,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -34014,7 +34014,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -34052,7 +34052,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -34090,7 +34090,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -34128,7 +34128,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -34166,7 +34166,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -34204,7 +34204,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -34242,7 +34242,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -34280,7 +34280,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -34318,7 +34318,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -34356,7 +34356,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -34394,7 +34394,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -34432,7 +34432,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -34470,7 +34470,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -34508,7 +34508,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -34546,7 +34546,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -34584,7 +34584,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -34622,7 +34622,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -34660,7 +34660,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -34698,7 +34698,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -34736,7 +34736,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -34774,7 +34774,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -34812,7 +34812,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -34850,7 +34850,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -34888,7 +34888,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -34926,7 +34926,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -34964,7 +34964,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -35002,7 +35002,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -35040,7 +35040,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -35078,7 +35078,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -35116,7 +35116,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -35154,7 +35154,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -35192,7 +35192,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -35230,7 +35230,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -35268,7 +35268,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -35306,7 +35306,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -35382,7 +35382,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -35420,7 +35420,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -35458,7 +35458,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -35496,7 +35496,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -35534,7 +35534,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -35572,7 +35572,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -35610,7 +35610,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -35648,7 +35648,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -35686,7 +35686,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -35724,7 +35724,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -35762,7 +35762,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -35800,7 +35800,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -35838,7 +35838,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -35876,7 +35876,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -35914,7 +35914,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -35952,7 +35952,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -35990,7 +35990,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -36028,7 +36028,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -36066,7 +36066,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -36104,7 +36104,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -36142,7 +36142,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -36180,7 +36180,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -36218,7 +36218,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -36256,7 +36256,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -36294,7 +36294,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -36332,7 +36332,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -36370,7 +36370,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -36408,7 +36408,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -36446,7 +36446,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -36484,7 +36484,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -36522,7 +36522,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -36560,7 +36560,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -36598,7 +36598,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -36636,7 +36636,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -36674,7 +36674,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -36712,7 +36712,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -36750,7 +36750,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -36788,7 +36788,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -36826,7 +36826,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -36864,7 +36864,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -36902,7 +36902,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -36940,7 +36940,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -36978,7 +36978,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -37016,7 +37016,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -37054,7 +37054,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -37130,7 +37130,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -37168,7 +37168,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -37206,7 +37206,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -37244,7 +37244,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -37282,7 +37282,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -37320,7 +37320,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -37358,7 +37358,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -37396,7 +37396,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -37434,7 +37434,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -37472,7 +37472,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -37510,7 +37510,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -37548,7 +37548,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -37586,7 +37586,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -37624,7 +37624,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -37662,7 +37662,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -37700,7 +37700,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -37738,7 +37738,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -37776,7 +37776,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -37814,7 +37814,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -37852,7 +37852,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -37890,7 +37890,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -37928,7 +37928,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -37966,7 +37966,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -38004,7 +38004,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -38042,7 +38042,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -38080,7 +38080,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -38118,7 +38118,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -38156,7 +38156,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -38194,7 +38194,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -38232,7 +38232,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -38270,7 +38270,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -38308,7 +38308,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -38346,7 +38346,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -38384,7 +38384,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -38422,7 +38422,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -38460,7 +38460,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -38498,7 +38498,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -38536,7 +38536,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -38574,7 +38574,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H480" s="4" t="inlineStr"/>
@@ -38612,7 +38612,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H481" s="4" t="inlineStr"/>
@@ -38650,7 +38650,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H482" s="4" t="inlineStr"/>
@@ -38688,7 +38688,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H483" s="4" t="inlineStr"/>
@@ -38726,7 +38726,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H484" s="4" t="inlineStr"/>
@@ -38764,7 +38764,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H485" s="4" t="inlineStr"/>
@@ -38802,7 +38802,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H486" s="4" t="inlineStr"/>
@@ -38840,7 +38840,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H487" s="4" t="inlineStr"/>
@@ -38878,7 +38878,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H488" s="4" t="inlineStr"/>
@@ -38916,7 +38916,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H489" s="4" t="inlineStr"/>
@@ -38954,7 +38954,7 @@
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H490" s="4" t="inlineStr"/>
@@ -38992,7 +38992,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H491" s="4" t="inlineStr"/>
@@ -39030,7 +39030,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H492" s="4" t="inlineStr"/>
@@ -39068,7 +39068,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H493" s="4" t="inlineStr"/>
@@ -39106,7 +39106,7 @@
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H494" s="4" t="inlineStr"/>
@@ -39144,7 +39144,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H495" s="4" t="inlineStr"/>
@@ -39182,7 +39182,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H496" s="4" t="inlineStr"/>
@@ -39220,7 +39220,7 @@
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H497" s="4" t="inlineStr"/>
@@ -39258,7 +39258,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H498" s="4" t="inlineStr"/>
@@ -39296,7 +39296,7 @@
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H499" s="4" t="inlineStr"/>
@@ -39334,7 +39334,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H500" s="4" t="inlineStr"/>
@@ -39372,7 +39372,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H501" s="4" t="inlineStr"/>
@@ -39410,7 +39410,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H502" s="4" t="inlineStr"/>
@@ -39448,7 +39448,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H503" s="4" t="inlineStr"/>
@@ -39486,7 +39486,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H504" s="4" t="inlineStr"/>
@@ -39524,7 +39524,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H505" s="4" t="inlineStr"/>
@@ -39562,7 +39562,7 @@
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H506" s="4" t="inlineStr"/>
@@ -39600,7 +39600,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H507" s="4" t="inlineStr"/>
@@ -39638,7 +39638,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H508" s="4" t="inlineStr"/>
@@ -39676,7 +39676,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H509" s="4" t="inlineStr"/>
@@ -39714,7 +39714,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H510" s="4" t="inlineStr"/>
@@ -39752,7 +39752,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H511" s="4" t="inlineStr"/>
@@ -39790,7 +39790,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H512" s="4" t="inlineStr"/>
@@ -39828,7 +39828,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H513" s="4" t="inlineStr"/>
@@ -39866,7 +39866,7 @@
       </c>
       <c r="G514" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H514" s="4" t="inlineStr"/>
@@ -39904,7 +39904,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H515" s="4" t="inlineStr"/>
@@ -39942,7 +39942,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H516" s="4" t="inlineStr"/>
@@ -39980,7 +39980,7 @@
       </c>
       <c r="G517" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H517" s="4" t="inlineStr"/>
@@ -40018,7 +40018,7 @@
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H518" s="4" t="inlineStr"/>
@@ -40056,7 +40056,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H519" s="4" t="inlineStr"/>
@@ -40094,7 +40094,7 @@
       </c>
       <c r="G520" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:08</t>
+          <t>2026-06-23 16:34:19</t>
         </is>
       </c>
       <c r="H520" s="4" t="inlineStr"/>
@@ -40118,7 +40118,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
@@ -40179,7 +40179,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>TC_GEN_007</t>
+          <t>TC_GEN_003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -40189,7 +40189,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>test_navigation_between_screens</t>
+          <t>test_home_page_load</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -40204,17 +40204,17 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>29.99</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:03:31</t>
+          <t>2026-06-23 16:31:25</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>driver = &lt;appium.webdriver.webdriver.WebDriver (session="5d941e00-69e0-4516-8ef1-9aad1eb798d1")&gt;
+          <t>driver = &lt;appium.webdriver.webdriver.WebDriver (session="780dd579-ad7d-405b-92c8-18302ab263c6")&gt;
     @pytest.fixture(scope="function")
     def auth_driver(driver):
         """Fixture to launch app and log in automatically with test credentials."""
@@ -40245,8 +40245,8 @@
 /opt/hostedtoolcache/Python/3.11.15/x64/lib/python3.11/site-packages/selenium/webdriver/remote/webdriver.py:492: in execute
     self.error_handler.check_response(response)
 _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ _ 
-self = &lt;appium.webdriver.errorhandler.MobileErrorHandler object at 0x7f904310df50&gt;
-response = {'status': 500, 'value': '{"value":{"error":"unknown error","message":"Timed out after 10504ms waiting for the root Ac...r2.core.AccessibilityNodeInfoDumper.findNodesUsingXpath2(AccessibilityNodeInfoDumper.java:327)\\n\\t... 33 more\\n"}}'}
+self = &lt;appium.webdriver.errorhandler.MobileErrorHandler object at 0x7f052231b410&gt;
+response = {'status': 500, 'value': '{"value":{"error":"unknown error","message":"Timed out after 10510ms waiting for the root Ac...r2.core.AccessibilityNodeInfoDumper.findNodesUsingXpath2(AccessibilityNodeInfoDumper.java:327)\\n\\t... 33 more\\n"}}'}
     def check_response(self, response: Dict[str, Any]) -&gt; None:
         """
         https://www.w3.org/TR/webdriver/#errors
@@ -40287,9 +40287,9 @@
                 alert_text=value.get('data'),
             )
 &gt;       raise exception_class(msg=message, stacktrace=format_stacktrace(stacktrace))
-E       selenium.common.exceptions.WebDriverException: Message: Timed out after 10504ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work. Try changing the 'enforceXPath1' driver setting to 'true' in order to workaround the problem.
+E       selenium.common.exceptions.WebDriverException: Message: Timed out after 10510ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work. Try changing the 'enforceXPath1' driver setting to 'true' in order to workaround the problem.
 E       Stacktrace:
-E       io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: Timed out after 10504ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work. Try changing the 'enforceXPath1' driver setting to 'true' in order to workaround the problem.
+E       io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: Timed out after 10510ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work. Try changing the 'enforceXPath1' driver setting to 'true' in order to workaround the problem.
 E       	at io.appium.uiautomator2.core.AccessibilityNodeInfoDumper.findNodesUsingXpath2(AccessibilityNodeInfoDumper.java:366)
 E       	at io.appium.uiautomator2.core.AccessibilityNodeInfoDumper.findNodes(AccessibilityNodeInfoDumper.java:378)
 E       	at io.appium.uiautomator2.utils.ElementLocationHelpers.getXPathNodeMatch(ElementLocationHelpers.java:124)
@@ -40324,7 +40324,7 @@
 E       	at io.netty.util.internal.ThreadExecutorMap$2.run(ThreadExecutorMap.java:74)
 E       	at io.netty.util.concurrent.FastThreadLocalRunnable.run(FastThreadLocalRunnable.java:30)
 E       	at java.lang.Thread.run(Thread.java:919)
-E       Caused by: io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: Timed out after 10504ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work
+E       Caused by: io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: Timed out after 10510ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work
 E       	at io.appium.uiautomator2.utils.AXWindowHelpers.getActiveWindowRoot(AXWindowHelpers.java:107)
 E       	at io.appium.uiautomator2.utils.AXWindowHelpers.retrieveWindowRoots(AXWindowHelpers.java:87)
 E       	at io.appium.uiautomator2.utils.AXWindowHelpers.getCachedWindowRoots(AXWindowHelpers.java:68)
@@ -40524,7 +40524,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>2026-06-23 16:04:09</t>
+          <t>2026-06-23 16:34:20</t>
         </is>
       </c>
     </row>
@@ -40595,7 +40595,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>TC_GEN_007</t>
+          <t>TC_GEN_003</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -40605,7 +40605,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>driver = &lt;appium.webdriver.webdriver.WebDriver (session="5d941e00-69e0-4516-8ef1-9aad1eb798d1")&gt;</t>
+          <t>driver = &lt;appium.webdriver.webdriver.WebDriver (session="780dd579-ad7d-405b-92c8-18302ab263c6")&gt;</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">

--- a/reports/latest/android/Excel/Automation_Test_Report.xlsx
+++ b/reports/latest/android/Excel/Automation_Test_Report.xlsx
@@ -594,12 +594,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:37:54</t>
+          <t>2026-06-24 04:16:07</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -632,12 +632,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>28.26</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:38:22</t>
+          <t>2026-06-24 04:16:40</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -670,12 +670,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>26.61</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:38:48</t>
+          <t>2026-06-24 04:17:13</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -708,12 +708,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>29.40</t>
+          <t>33.90</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:39:18</t>
+          <t>2026-06-24 04:17:46</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -746,12 +746,12 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>32.07</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:39:46</t>
+          <t>2026-06-24 04:18:19</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -784,12 +784,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:40:14</t>
+          <t>2026-06-24 04:18:51</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -822,12 +822,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>34.93</t>
+          <t>39.17</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:40:49</t>
+          <t>2026-06-24 04:19:30</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -860,12 +860,12 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>31.43</t>
+          <t>35.95</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -898,12 +898,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -941,7 +941,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -979,7 +979,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -6223,7 +6223,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -7477,7 +7477,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -7553,7 +7553,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -7667,7 +7667,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -8427,7 +8427,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -8465,7 +8465,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -9073,7 +9073,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -9567,7 +9567,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -9795,7 +9795,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -9947,7 +9947,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -9985,7 +9985,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -10023,7 +10023,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -10061,7 +10061,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -10099,7 +10099,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -10213,7 +10213,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -10251,7 +10251,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -10441,7 +10441,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -10517,7 +10517,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -10555,7 +10555,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -10593,7 +10593,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -10669,7 +10669,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -10783,7 +10783,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -10897,7 +10897,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -10935,7 +10935,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -11011,7 +11011,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -11277,7 +11277,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -11353,7 +11353,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -11505,7 +11505,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -11543,7 +11543,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -11657,7 +11657,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -11733,7 +11733,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -11847,7 +11847,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -11923,7 +11923,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -12037,7 +12037,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -12075,7 +12075,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -12189,7 +12189,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -12227,7 +12227,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -12265,7 +12265,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -12303,7 +12303,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -12341,7 +12341,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -12531,7 +12531,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -12607,7 +12607,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -12645,7 +12645,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -12721,7 +12721,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -12911,7 +12911,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -12949,7 +12949,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -12987,7 +12987,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -13063,7 +13063,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -13101,7 +13101,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -13291,7 +13291,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -13443,7 +13443,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -13481,7 +13481,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -13519,7 +13519,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -13595,7 +13595,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -13709,7 +13709,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -13747,7 +13747,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -13785,7 +13785,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -13823,7 +13823,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -13861,7 +13861,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -14089,7 +14089,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -14127,7 +14127,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -14165,7 +14165,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -14203,7 +14203,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -14241,7 +14241,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -14431,7 +14431,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -14469,7 +14469,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -14545,7 +14545,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -14659,7 +14659,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -14697,7 +14697,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -14735,7 +14735,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -14773,7 +14773,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -14811,7 +14811,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -14849,7 +14849,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -14887,7 +14887,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -14925,7 +14925,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -14963,7 +14963,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -15001,7 +15001,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -15039,7 +15039,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -15153,7 +15153,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -15191,7 +15191,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -15267,7 +15267,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -15305,7 +15305,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -15381,7 +15381,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -15419,7 +15419,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -15457,7 +15457,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -15495,7 +15495,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -15571,7 +15571,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -15609,7 +15609,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -15685,7 +15685,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -15723,7 +15723,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -15799,7 +15799,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -15837,7 +15837,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -15875,7 +15875,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -15951,7 +15951,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -15989,7 +15989,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -16065,7 +16065,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -16103,7 +16103,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -16141,7 +16141,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -16179,7 +16179,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -16217,7 +16217,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -16255,7 +16255,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -16293,7 +16293,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -16407,7 +16407,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -16483,7 +16483,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -16521,7 +16521,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -16597,7 +16597,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -16673,7 +16673,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -16711,7 +16711,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -16749,7 +16749,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -16825,7 +16825,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -16863,7 +16863,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -16939,7 +16939,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -16977,7 +16977,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -17053,7 +17053,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -17091,7 +17091,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -17129,7 +17129,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -17167,7 +17167,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -17205,7 +17205,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -17243,7 +17243,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -17319,7 +17319,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -17357,7 +17357,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -17433,7 +17433,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -17471,7 +17471,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -17509,7 +17509,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -17547,7 +17547,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -17585,7 +17585,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -17737,7 +17737,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -17775,7 +17775,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -17813,7 +17813,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -17851,7 +17851,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -17965,7 +17965,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -18003,7 +18003,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -18079,7 +18079,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -18117,7 +18117,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -18155,7 +18155,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -18231,7 +18231,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -18269,7 +18269,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -18307,7 +18307,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -18345,7 +18345,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -18383,7 +18383,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -18421,7 +18421,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -18459,7 +18459,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -18497,7 +18497,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -18535,7 +18535,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -18573,7 +18573,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -18611,7 +18611,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -18649,7 +18649,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -18687,7 +18687,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H480" s="4" t="inlineStr"/>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H481" s="4" t="inlineStr"/>
@@ -18763,7 +18763,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H482" s="4" t="inlineStr"/>
@@ -18801,7 +18801,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H483" s="4" t="inlineStr"/>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H484" s="4" t="inlineStr"/>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H485" s="4" t="inlineStr"/>
@@ -18915,7 +18915,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H486" s="4" t="inlineStr"/>
@@ -18953,7 +18953,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H487" s="4" t="inlineStr"/>
@@ -18991,7 +18991,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H488" s="4" t="inlineStr"/>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H489" s="4" t="inlineStr"/>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H490" s="4" t="inlineStr"/>
@@ -19105,7 +19105,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H491" s="4" t="inlineStr"/>
@@ -19143,7 +19143,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H492" s="4" t="inlineStr"/>
@@ -19181,7 +19181,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H493" s="4" t="inlineStr"/>
@@ -19219,7 +19219,7 @@
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H494" s="4" t="inlineStr"/>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H495" s="4" t="inlineStr"/>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H496" s="4" t="inlineStr"/>
@@ -19333,7 +19333,7 @@
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H497" s="4" t="inlineStr"/>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H498" s="4" t="inlineStr"/>
@@ -19409,7 +19409,7 @@
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H499" s="4" t="inlineStr"/>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H500" s="4" t="inlineStr"/>
@@ -19485,7 +19485,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H501" s="4" t="inlineStr"/>
@@ -19523,7 +19523,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H502" s="4" t="inlineStr"/>
@@ -19561,7 +19561,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H503" s="4" t="inlineStr"/>
@@ -19599,7 +19599,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H504" s="4" t="inlineStr"/>
@@ -19637,7 +19637,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H505" s="4" t="inlineStr"/>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H506" s="4" t="inlineStr"/>
@@ -19713,7 +19713,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H507" s="4" t="inlineStr"/>
@@ -19751,7 +19751,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H508" s="4" t="inlineStr"/>
@@ -19789,7 +19789,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H509" s="4" t="inlineStr"/>
@@ -19827,7 +19827,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H510" s="4" t="inlineStr"/>
@@ -19865,7 +19865,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H511" s="4" t="inlineStr"/>
@@ -19903,7 +19903,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H512" s="4" t="inlineStr"/>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H513" s="4" t="inlineStr"/>
@@ -19979,7 +19979,7 @@
       </c>
       <c r="G514" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H514" s="4" t="inlineStr"/>
@@ -20017,7 +20017,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H515" s="4" t="inlineStr"/>
@@ -20055,7 +20055,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H516" s="4" t="inlineStr"/>
@@ -20093,7 +20093,7 @@
       </c>
       <c r="G517" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H517" s="4" t="inlineStr"/>
@@ -20131,7 +20131,7 @@
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H518" s="4" t="inlineStr"/>
@@ -20169,7 +20169,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H519" s="4" t="inlineStr"/>
@@ -20207,7 +20207,7 @@
       </c>
       <c r="G520" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H520" s="4" t="inlineStr"/>
@@ -20245,7 +20245,7 @@
       </c>
       <c r="G521" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H521" s="4" t="inlineStr"/>
@@ -20350,12 +20350,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:37:54</t>
+          <t>2026-06-24 04:16:07</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -20388,12 +20388,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>28.26</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:38:22</t>
+          <t>2026-06-24 04:16:40</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -20426,12 +20426,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>26.61</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:38:48</t>
+          <t>2026-06-24 04:17:13</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -20464,12 +20464,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>29.40</t>
+          <t>33.90</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:39:18</t>
+          <t>2026-06-24 04:17:46</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -20502,12 +20502,12 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>32.07</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:39:46</t>
+          <t>2026-06-24 04:18:19</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -20540,12 +20540,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:40:14</t>
+          <t>2026-06-24 04:18:51</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -20578,12 +20578,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>34.93</t>
+          <t>39.17</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:40:49</t>
+          <t>2026-06-24 04:19:30</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -20616,12 +20616,12 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>31.43</t>
+          <t>35.95</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -20654,12 +20654,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -20697,7 +20697,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -20735,7 +20735,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -20773,7 +20773,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -20811,7 +20811,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -20849,7 +20849,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -20887,7 +20887,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -20925,7 +20925,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -20963,7 +20963,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -21001,7 +21001,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -21039,7 +21039,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -21115,7 +21115,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -21153,7 +21153,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -21191,7 +21191,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -21229,7 +21229,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -21267,7 +21267,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -21305,7 +21305,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -21343,7 +21343,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -21419,7 +21419,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -21495,7 +21495,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -21533,7 +21533,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -21571,7 +21571,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -21647,7 +21647,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -21685,7 +21685,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -21723,7 +21723,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -21761,7 +21761,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -21875,7 +21875,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -21913,7 +21913,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -21951,7 +21951,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -21989,7 +21989,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -22027,7 +22027,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -22065,7 +22065,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -22103,7 +22103,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -22141,7 +22141,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -22179,7 +22179,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -22217,7 +22217,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -22255,7 +22255,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -22293,7 +22293,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -22331,7 +22331,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -22369,7 +22369,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -22407,7 +22407,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -22445,7 +22445,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -22521,7 +22521,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -22559,7 +22559,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -22597,7 +22597,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -22635,7 +22635,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -22711,7 +22711,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -22749,7 +22749,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -22787,7 +22787,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -22825,7 +22825,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -22901,7 +22901,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -22939,7 +22939,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -22977,7 +22977,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -23015,7 +23015,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -23053,7 +23053,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -23091,7 +23091,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -23167,7 +23167,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -23205,7 +23205,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -23243,7 +23243,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -23281,7 +23281,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -23319,7 +23319,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -23357,7 +23357,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -23395,7 +23395,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -23433,7 +23433,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -23509,7 +23509,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -23547,7 +23547,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -23585,7 +23585,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -23623,7 +23623,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -23661,7 +23661,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -23699,7 +23699,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -23737,7 +23737,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -23775,7 +23775,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -23813,7 +23813,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -23851,7 +23851,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -23889,7 +23889,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -23927,7 +23927,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -23965,7 +23965,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -24003,7 +24003,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -24041,7 +24041,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -24079,7 +24079,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -24117,7 +24117,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -24193,7 +24193,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -24231,7 +24231,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -24307,7 +24307,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -24345,7 +24345,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -24383,7 +24383,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -24421,7 +24421,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -24459,7 +24459,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -24497,7 +24497,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -24535,7 +24535,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -24573,7 +24573,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -24611,7 +24611,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -24649,7 +24649,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -24687,7 +24687,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -24725,7 +24725,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -24763,7 +24763,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -24801,7 +24801,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -24839,7 +24839,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -24877,7 +24877,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -24915,7 +24915,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -24953,7 +24953,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -24991,7 +24991,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -25029,7 +25029,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -25067,7 +25067,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -25105,7 +25105,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -25143,7 +25143,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -25219,7 +25219,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -25257,7 +25257,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -25295,7 +25295,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -25333,7 +25333,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -25371,7 +25371,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -25409,7 +25409,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -25447,7 +25447,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -25485,7 +25485,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -25523,7 +25523,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -25561,7 +25561,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -25599,7 +25599,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -25637,7 +25637,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -25675,7 +25675,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -25713,7 +25713,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -25751,7 +25751,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -25789,7 +25789,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -25827,7 +25827,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -25865,7 +25865,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -25903,7 +25903,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -25941,7 +25941,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -25979,7 +25979,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -26017,7 +26017,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -26055,7 +26055,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -26093,7 +26093,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -26169,7 +26169,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -26207,7 +26207,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -26245,7 +26245,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -26359,7 +26359,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -26397,7 +26397,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -26435,7 +26435,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -26473,7 +26473,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -26511,7 +26511,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -26549,7 +26549,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -26587,7 +26587,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -26625,7 +26625,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -26663,7 +26663,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -26701,7 +26701,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -26739,7 +26739,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -26815,7 +26815,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -26853,7 +26853,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -26891,7 +26891,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -26929,7 +26929,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -26967,7 +26967,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -27005,7 +27005,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -27043,7 +27043,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -27081,7 +27081,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -27119,7 +27119,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -27157,7 +27157,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -27233,7 +27233,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -27271,7 +27271,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -27309,7 +27309,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -27347,7 +27347,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -27385,7 +27385,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -27423,7 +27423,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -27461,7 +27461,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -27499,7 +27499,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -27537,7 +27537,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -27575,7 +27575,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -27613,7 +27613,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -27651,7 +27651,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -27689,7 +27689,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -27727,7 +27727,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -27765,7 +27765,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -27803,7 +27803,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -27841,7 +27841,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -27879,7 +27879,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -27917,7 +27917,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -27955,7 +27955,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -27993,7 +27993,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -28031,7 +28031,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -28107,7 +28107,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -28145,7 +28145,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -28183,7 +28183,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -28221,7 +28221,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -28259,7 +28259,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -28297,7 +28297,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -28373,7 +28373,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -28411,7 +28411,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -28449,7 +28449,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -28487,7 +28487,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -28525,7 +28525,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -28563,7 +28563,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -28601,7 +28601,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -28639,7 +28639,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -28677,7 +28677,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -28715,7 +28715,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -28753,7 +28753,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -28791,7 +28791,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -28829,7 +28829,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -28867,7 +28867,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -28905,7 +28905,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -28981,7 +28981,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -29019,7 +29019,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -29057,7 +29057,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -29095,7 +29095,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -29133,7 +29133,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -29171,7 +29171,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -29209,7 +29209,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -29247,7 +29247,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -29285,7 +29285,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -29323,7 +29323,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -29361,7 +29361,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -29399,7 +29399,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -29437,7 +29437,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -29475,7 +29475,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -29513,7 +29513,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -29551,7 +29551,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -29627,7 +29627,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -29665,7 +29665,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -29703,7 +29703,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -29741,7 +29741,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -29779,7 +29779,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -29855,7 +29855,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -29893,7 +29893,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -29931,7 +29931,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -29969,7 +29969,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -30007,7 +30007,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -30045,7 +30045,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -30083,7 +30083,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -30121,7 +30121,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -30159,7 +30159,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -30197,7 +30197,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -30235,7 +30235,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -30273,7 +30273,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -30311,7 +30311,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -30349,7 +30349,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -30425,7 +30425,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -30463,7 +30463,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -30501,7 +30501,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -30539,7 +30539,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -30577,7 +30577,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -30615,7 +30615,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -30653,7 +30653,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -30729,7 +30729,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -30767,7 +30767,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -30805,7 +30805,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -30843,7 +30843,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -30881,7 +30881,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -30919,7 +30919,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -30957,7 +30957,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -30995,7 +30995,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -31033,7 +31033,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -31071,7 +31071,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -31109,7 +31109,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -31147,7 +31147,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -31185,7 +31185,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -31223,7 +31223,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -31261,7 +31261,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -31299,7 +31299,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -31337,7 +31337,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -31375,7 +31375,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -31413,7 +31413,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -31451,7 +31451,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -31489,7 +31489,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -31527,7 +31527,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -31603,7 +31603,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -31641,7 +31641,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -31679,7 +31679,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -31717,7 +31717,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -31755,7 +31755,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -31793,7 +31793,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -31831,7 +31831,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -31869,7 +31869,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -31907,7 +31907,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -31945,7 +31945,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -31983,7 +31983,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -32021,7 +32021,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -32059,7 +32059,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -32097,7 +32097,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -32135,7 +32135,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -32173,7 +32173,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -32211,7 +32211,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -32249,7 +32249,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -32325,7 +32325,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -32363,7 +32363,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -32401,7 +32401,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -32477,7 +32477,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -32515,7 +32515,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -32553,7 +32553,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -32591,7 +32591,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -32629,7 +32629,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -32667,7 +32667,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -32705,7 +32705,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -32743,7 +32743,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -32819,7 +32819,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -32857,7 +32857,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -32895,7 +32895,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -32933,7 +32933,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -32971,7 +32971,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -33009,7 +33009,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -33047,7 +33047,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -33085,7 +33085,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -33123,7 +33123,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -33161,7 +33161,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -33199,7 +33199,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -33237,7 +33237,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -33275,7 +33275,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -33351,7 +33351,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -33389,7 +33389,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -33427,7 +33427,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -33465,7 +33465,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -33503,7 +33503,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -33541,7 +33541,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -33579,7 +33579,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -33617,7 +33617,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -33655,7 +33655,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -33693,7 +33693,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -33731,7 +33731,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -33769,7 +33769,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -33807,7 +33807,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -33845,7 +33845,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -33883,7 +33883,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -33921,7 +33921,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -33959,7 +33959,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -33997,7 +33997,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -34035,7 +34035,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -34073,7 +34073,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -34111,7 +34111,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -34149,7 +34149,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -34225,7 +34225,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -34263,7 +34263,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -34301,7 +34301,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -34339,7 +34339,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -34377,7 +34377,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -34415,7 +34415,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -34453,7 +34453,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -34491,7 +34491,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -34529,7 +34529,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -34567,7 +34567,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -34605,7 +34605,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -34643,7 +34643,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -34681,7 +34681,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -34719,7 +34719,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -34757,7 +34757,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -34795,7 +34795,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -34833,7 +34833,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -34871,7 +34871,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -34909,7 +34909,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -34947,7 +34947,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -34985,7 +34985,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -35023,7 +35023,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -35099,7 +35099,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -35137,7 +35137,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -35175,7 +35175,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -35213,7 +35213,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -35251,7 +35251,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -35289,7 +35289,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -35327,7 +35327,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -35365,7 +35365,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -35403,7 +35403,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -35441,7 +35441,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -35479,7 +35479,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -35517,7 +35517,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -35555,7 +35555,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -35593,7 +35593,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -35631,7 +35631,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -35669,7 +35669,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -35707,7 +35707,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:20</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -35745,7 +35745,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -35783,7 +35783,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -35821,7 +35821,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -35859,7 +35859,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -35897,7 +35897,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -35973,7 +35973,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -36011,7 +36011,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -36087,7 +36087,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -36125,7 +36125,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -36163,7 +36163,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -36201,7 +36201,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -36239,7 +36239,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -36277,7 +36277,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -36315,7 +36315,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -36353,7 +36353,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -36391,7 +36391,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -36429,7 +36429,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -36467,7 +36467,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -36505,7 +36505,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -36581,7 +36581,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -36619,7 +36619,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -36657,7 +36657,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -36695,7 +36695,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -36733,7 +36733,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -36771,7 +36771,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -36847,7 +36847,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -36885,7 +36885,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -36923,7 +36923,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -36961,7 +36961,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -36999,7 +36999,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -37037,7 +37037,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -37075,7 +37075,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -37113,7 +37113,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -37151,7 +37151,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -37189,7 +37189,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -37227,7 +37227,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -37265,7 +37265,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -37303,7 +37303,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -37341,7 +37341,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -37379,7 +37379,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -37417,7 +37417,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -37455,7 +37455,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -37493,7 +37493,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -37531,7 +37531,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -37569,7 +37569,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -37607,7 +37607,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -37645,7 +37645,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -37721,7 +37721,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -37759,7 +37759,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -37797,7 +37797,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -37835,7 +37835,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -37873,7 +37873,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -37911,7 +37911,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -37949,7 +37949,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -37987,7 +37987,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -38025,7 +38025,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -38063,7 +38063,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -38101,7 +38101,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -38139,7 +38139,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -38177,7 +38177,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -38215,7 +38215,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -38253,7 +38253,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -38291,7 +38291,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -38329,7 +38329,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -38367,7 +38367,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -38405,7 +38405,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -38443,7 +38443,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H480" s="4" t="inlineStr"/>
@@ -38481,7 +38481,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H481" s="4" t="inlineStr"/>
@@ -38519,7 +38519,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H482" s="4" t="inlineStr"/>
@@ -38557,7 +38557,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H483" s="4" t="inlineStr"/>
@@ -38595,7 +38595,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H484" s="4" t="inlineStr"/>
@@ -38633,7 +38633,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H485" s="4" t="inlineStr"/>
@@ -38671,7 +38671,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H486" s="4" t="inlineStr"/>
@@ -38709,7 +38709,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H487" s="4" t="inlineStr"/>
@@ -38747,7 +38747,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H488" s="4" t="inlineStr"/>
@@ -38785,7 +38785,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H489" s="4" t="inlineStr"/>
@@ -38823,7 +38823,7 @@
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H490" s="4" t="inlineStr"/>
@@ -38861,7 +38861,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H491" s="4" t="inlineStr"/>
@@ -38899,7 +38899,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:06</t>
         </is>
       </c>
       <c r="H492" s="4" t="inlineStr"/>
@@ -38937,7 +38937,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H493" s="4" t="inlineStr"/>
@@ -38975,7 +38975,7 @@
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H494" s="4" t="inlineStr"/>
@@ -39013,7 +39013,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H495" s="4" t="inlineStr"/>
@@ -39051,7 +39051,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H496" s="4" t="inlineStr"/>
@@ -39089,7 +39089,7 @@
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H497" s="4" t="inlineStr"/>
@@ -39127,7 +39127,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H498" s="4" t="inlineStr"/>
@@ -39165,7 +39165,7 @@
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H499" s="4" t="inlineStr"/>
@@ -39203,7 +39203,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H500" s="4" t="inlineStr"/>
@@ -39241,7 +39241,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H501" s="4" t="inlineStr"/>
@@ -39279,7 +39279,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H502" s="4" t="inlineStr"/>
@@ -39317,7 +39317,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H503" s="4" t="inlineStr"/>
@@ -39355,7 +39355,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H504" s="4" t="inlineStr"/>
@@ -39393,7 +39393,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H505" s="4" t="inlineStr"/>
@@ -39431,7 +39431,7 @@
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H506" s="4" t="inlineStr"/>
@@ -39469,7 +39469,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H507" s="4" t="inlineStr"/>
@@ -39507,7 +39507,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H508" s="4" t="inlineStr"/>
@@ -39545,7 +39545,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H509" s="4" t="inlineStr"/>
@@ -39583,7 +39583,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H510" s="4" t="inlineStr"/>
@@ -39621,7 +39621,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H511" s="4" t="inlineStr"/>
@@ -39659,7 +39659,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H512" s="4" t="inlineStr"/>
@@ -39697,7 +39697,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H513" s="4" t="inlineStr"/>
@@ -39735,7 +39735,7 @@
       </c>
       <c r="G514" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H514" s="4" t="inlineStr"/>
@@ -39773,7 +39773,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H515" s="4" t="inlineStr"/>
@@ -39811,7 +39811,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H516" s="4" t="inlineStr"/>
@@ -39849,7 +39849,7 @@
       </c>
       <c r="G517" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H517" s="4" t="inlineStr"/>
@@ -39887,7 +39887,7 @@
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H518" s="4" t="inlineStr"/>
@@ -39925,7 +39925,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H519" s="4" t="inlineStr"/>
@@ -39963,7 +39963,7 @@
       </c>
       <c r="G520" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H520" s="4" t="inlineStr"/>
@@ -40001,7 +40001,7 @@
       </c>
       <c r="G521" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:07</t>
         </is>
       </c>
       <c r="H521" s="4" t="inlineStr"/>
@@ -40272,7 +40272,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>2026-06-24 02:41:21</t>
+          <t>2026-06-24 04:20:08</t>
         </is>
       </c>
     </row>

--- a/reports/latest/android/Excel/Automation_Test_Report.xlsx
+++ b/reports/latest/android/Excel/Automation_Test_Report.xlsx
@@ -594,12 +594,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>21.15</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:16:07</t>
+          <t>2026-06-24 04:38:26</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -632,12 +632,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:16:40</t>
+          <t>2026-06-24 04:38:57</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -670,12 +670,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:17:13</t>
+          <t>2026-06-24 04:39:26</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -708,12 +708,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>33.90</t>
+          <t>59.63</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:17:46</t>
+          <t>2026-06-24 04:40:00</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -746,12 +746,12 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>32.07</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:18:19</t>
+          <t>2026-06-24 04:41:01</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -784,12 +784,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>29.56</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:18:51</t>
+          <t>2026-06-24 04:41:30</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -822,12 +822,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>36.93</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:19:30</t>
+          <t>2026-06-24 04:42:07</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -860,12 +860,12 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>33.00</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -898,12 +898,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -941,7 +941,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -979,7 +979,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -6223,7 +6223,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -7477,7 +7477,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -7553,7 +7553,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -7667,7 +7667,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -8427,7 +8427,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -8465,7 +8465,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -9073,7 +9073,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -9567,7 +9567,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -9795,7 +9795,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -9947,7 +9947,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -9985,7 +9985,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -10023,7 +10023,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -10061,7 +10061,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -10099,7 +10099,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -10213,7 +10213,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -10251,7 +10251,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -10441,7 +10441,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -10517,7 +10517,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -10555,7 +10555,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -10593,7 +10593,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -10669,7 +10669,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -10783,7 +10783,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -10897,7 +10897,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -10935,7 +10935,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -11011,7 +11011,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -11277,7 +11277,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -11353,7 +11353,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -11505,7 +11505,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -11543,7 +11543,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -11657,7 +11657,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -11733,7 +11733,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -11847,7 +11847,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -11923,7 +11923,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -12037,7 +12037,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -12075,7 +12075,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -12189,7 +12189,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -12227,7 +12227,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -12265,7 +12265,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -12303,7 +12303,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -12341,7 +12341,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -12531,7 +12531,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -12607,7 +12607,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -12645,7 +12645,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -12721,7 +12721,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -12911,7 +12911,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -12949,7 +12949,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -12987,7 +12987,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -13063,7 +13063,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -13101,7 +13101,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -13291,7 +13291,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -13443,7 +13443,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -13481,7 +13481,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -13519,7 +13519,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -13595,7 +13595,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -13709,7 +13709,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -13747,7 +13747,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -13785,7 +13785,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -13823,7 +13823,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -13861,7 +13861,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -14089,7 +14089,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -14127,7 +14127,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -14165,7 +14165,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -14203,7 +14203,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -14241,7 +14241,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -14431,7 +14431,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -14469,7 +14469,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -14545,7 +14545,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -14659,7 +14659,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -14697,7 +14697,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -14735,7 +14735,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -14773,7 +14773,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -14811,7 +14811,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -14849,7 +14849,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -14887,7 +14887,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -14925,7 +14925,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -14963,7 +14963,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -15001,7 +15001,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -15039,7 +15039,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -15153,7 +15153,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -15191,7 +15191,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -15267,7 +15267,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -15305,7 +15305,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -15381,7 +15381,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -15419,7 +15419,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -15457,7 +15457,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -15495,7 +15495,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -15571,7 +15571,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -15609,7 +15609,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -15685,7 +15685,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -15723,7 +15723,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -15799,7 +15799,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -15837,7 +15837,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -15875,7 +15875,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -15951,7 +15951,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -15989,7 +15989,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -16065,7 +16065,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -16103,7 +16103,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -16141,7 +16141,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -16179,7 +16179,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -16217,7 +16217,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -16255,7 +16255,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -16293,7 +16293,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -16407,7 +16407,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -16483,7 +16483,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -16521,7 +16521,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -16597,7 +16597,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -16673,7 +16673,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -16711,7 +16711,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -16749,7 +16749,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -16825,7 +16825,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -16863,7 +16863,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -16939,7 +16939,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -16977,7 +16977,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -17053,7 +17053,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -17091,7 +17091,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -17129,7 +17129,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -17167,7 +17167,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -17205,7 +17205,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -17243,7 +17243,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -17319,7 +17319,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -17357,7 +17357,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -17433,7 +17433,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -17471,7 +17471,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -17509,7 +17509,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -17547,7 +17547,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -17585,7 +17585,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -17737,7 +17737,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -17775,7 +17775,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -17813,7 +17813,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -17851,7 +17851,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -17965,7 +17965,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -18003,7 +18003,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -18079,7 +18079,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -18117,7 +18117,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -18155,7 +18155,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -18231,7 +18231,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -18269,7 +18269,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -18307,7 +18307,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -18345,7 +18345,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -18383,7 +18383,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -18421,7 +18421,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -18459,7 +18459,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -18497,7 +18497,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -18535,7 +18535,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -18573,7 +18573,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -18611,7 +18611,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -18649,7 +18649,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -18687,7 +18687,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H480" s="4" t="inlineStr"/>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H481" s="4" t="inlineStr"/>
@@ -18763,7 +18763,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H482" s="4" t="inlineStr"/>
@@ -18801,7 +18801,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H483" s="4" t="inlineStr"/>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H484" s="4" t="inlineStr"/>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H485" s="4" t="inlineStr"/>
@@ -18915,7 +18915,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H486" s="4" t="inlineStr"/>
@@ -18953,7 +18953,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H487" s="4" t="inlineStr"/>
@@ -18991,7 +18991,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H488" s="4" t="inlineStr"/>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H489" s="4" t="inlineStr"/>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H490" s="4" t="inlineStr"/>
@@ -19105,7 +19105,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H491" s="4" t="inlineStr"/>
@@ -19143,7 +19143,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H492" s="4" t="inlineStr"/>
@@ -19181,7 +19181,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H493" s="4" t="inlineStr"/>
@@ -19219,7 +19219,7 @@
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H494" s="4" t="inlineStr"/>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H495" s="4" t="inlineStr"/>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H496" s="4" t="inlineStr"/>
@@ -19333,7 +19333,7 @@
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H497" s="4" t="inlineStr"/>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H498" s="4" t="inlineStr"/>
@@ -19409,7 +19409,7 @@
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H499" s="4" t="inlineStr"/>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H500" s="4" t="inlineStr"/>
@@ -19485,7 +19485,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H501" s="4" t="inlineStr"/>
@@ -19523,7 +19523,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H502" s="4" t="inlineStr"/>
@@ -19561,7 +19561,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H503" s="4" t="inlineStr"/>
@@ -19599,7 +19599,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H504" s="4" t="inlineStr"/>
@@ -19637,7 +19637,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H505" s="4" t="inlineStr"/>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H506" s="4" t="inlineStr"/>
@@ -19713,7 +19713,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H507" s="4" t="inlineStr"/>
@@ -19751,7 +19751,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H508" s="4" t="inlineStr"/>
@@ -19789,7 +19789,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H509" s="4" t="inlineStr"/>
@@ -19827,7 +19827,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H510" s="4" t="inlineStr"/>
@@ -19865,7 +19865,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H511" s="4" t="inlineStr"/>
@@ -19903,7 +19903,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H512" s="4" t="inlineStr"/>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H513" s="4" t="inlineStr"/>
@@ -19979,7 +19979,7 @@
       </c>
       <c r="G514" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H514" s="4" t="inlineStr"/>
@@ -20017,7 +20017,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H515" s="4" t="inlineStr"/>
@@ -20055,7 +20055,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H516" s="4" t="inlineStr"/>
@@ -20093,7 +20093,7 @@
       </c>
       <c r="G517" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H517" s="4" t="inlineStr"/>
@@ -20131,7 +20131,7 @@
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H518" s="4" t="inlineStr"/>
@@ -20169,7 +20169,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H519" s="4" t="inlineStr"/>
@@ -20207,7 +20207,7 @@
       </c>
       <c r="G520" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H520" s="4" t="inlineStr"/>
@@ -20245,7 +20245,7 @@
       </c>
       <c r="G521" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H521" s="4" t="inlineStr"/>
@@ -20350,12 +20350,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>21.15</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:16:07</t>
+          <t>2026-06-24 04:38:26</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -20388,12 +20388,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:16:40</t>
+          <t>2026-06-24 04:38:57</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -20426,12 +20426,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:17:13</t>
+          <t>2026-06-24 04:39:26</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -20464,12 +20464,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>33.90</t>
+          <t>59.63</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:17:46</t>
+          <t>2026-06-24 04:40:00</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -20502,12 +20502,12 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>32.07</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:18:19</t>
+          <t>2026-06-24 04:41:01</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -20540,12 +20540,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>29.56</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:18:51</t>
+          <t>2026-06-24 04:41:30</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -20578,12 +20578,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>36.93</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:19:30</t>
+          <t>2026-06-24 04:42:07</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -20616,12 +20616,12 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>33.00</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -20654,12 +20654,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -20697,7 +20697,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -20735,7 +20735,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -20773,7 +20773,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -20811,7 +20811,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -20849,7 +20849,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -20887,7 +20887,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -20925,7 +20925,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -20963,7 +20963,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -21001,7 +21001,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -21039,7 +21039,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -21115,7 +21115,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -21153,7 +21153,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -21191,7 +21191,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -21229,7 +21229,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -21267,7 +21267,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -21305,7 +21305,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -21343,7 +21343,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -21419,7 +21419,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -21495,7 +21495,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -21533,7 +21533,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -21571,7 +21571,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -21647,7 +21647,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -21685,7 +21685,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -21723,7 +21723,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -21761,7 +21761,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -21875,7 +21875,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -21913,7 +21913,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -21951,7 +21951,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -21989,7 +21989,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -22027,7 +22027,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -22065,7 +22065,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -22103,7 +22103,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -22141,7 +22141,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -22179,7 +22179,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -22217,7 +22217,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -22255,7 +22255,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -22293,7 +22293,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -22331,7 +22331,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -22369,7 +22369,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -22407,7 +22407,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -22445,7 +22445,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -22521,7 +22521,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -22559,7 +22559,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -22597,7 +22597,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -22635,7 +22635,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -22711,7 +22711,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -22749,7 +22749,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -22787,7 +22787,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -22825,7 +22825,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -22901,7 +22901,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -22939,7 +22939,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -22977,7 +22977,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -23015,7 +23015,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -23053,7 +23053,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -23091,7 +23091,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -23167,7 +23167,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -23205,7 +23205,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -23243,7 +23243,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -23281,7 +23281,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -23319,7 +23319,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -23357,7 +23357,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -23395,7 +23395,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -23433,7 +23433,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -23509,7 +23509,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -23547,7 +23547,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -23585,7 +23585,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -23623,7 +23623,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -23661,7 +23661,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -23699,7 +23699,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -23737,7 +23737,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -23775,7 +23775,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -23813,7 +23813,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -23851,7 +23851,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -23889,7 +23889,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -23927,7 +23927,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -23965,7 +23965,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -24003,7 +24003,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -24041,7 +24041,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -24079,7 +24079,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -24117,7 +24117,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -24193,7 +24193,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -24231,7 +24231,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -24307,7 +24307,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -24345,7 +24345,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -24383,7 +24383,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -24421,7 +24421,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -24459,7 +24459,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -24497,7 +24497,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -24535,7 +24535,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -24573,7 +24573,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -24611,7 +24611,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -24649,7 +24649,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -24687,7 +24687,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -24725,7 +24725,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -24763,7 +24763,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -24801,7 +24801,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -24839,7 +24839,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -24877,7 +24877,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -24915,7 +24915,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -24953,7 +24953,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -24991,7 +24991,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -25029,7 +25029,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -25067,7 +25067,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -25105,7 +25105,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -25143,7 +25143,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -25219,7 +25219,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -25257,7 +25257,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -25295,7 +25295,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -25333,7 +25333,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -25371,7 +25371,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -25409,7 +25409,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -25447,7 +25447,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -25485,7 +25485,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -25523,7 +25523,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -25561,7 +25561,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -25599,7 +25599,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -25637,7 +25637,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -25675,7 +25675,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -25713,7 +25713,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -25751,7 +25751,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -25789,7 +25789,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -25827,7 +25827,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -25865,7 +25865,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -25903,7 +25903,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -25941,7 +25941,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -25979,7 +25979,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -26017,7 +26017,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -26055,7 +26055,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -26093,7 +26093,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -26169,7 +26169,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -26207,7 +26207,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -26245,7 +26245,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -26359,7 +26359,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -26397,7 +26397,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -26435,7 +26435,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -26473,7 +26473,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -26511,7 +26511,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -26549,7 +26549,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -26587,7 +26587,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -26625,7 +26625,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -26663,7 +26663,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -26701,7 +26701,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -26739,7 +26739,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -26815,7 +26815,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -26853,7 +26853,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -26891,7 +26891,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -26929,7 +26929,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -26967,7 +26967,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -27005,7 +27005,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -27043,7 +27043,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -27081,7 +27081,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -27119,7 +27119,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -27157,7 +27157,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -27233,7 +27233,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -27271,7 +27271,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -27309,7 +27309,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -27347,7 +27347,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -27385,7 +27385,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -27423,7 +27423,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -27461,7 +27461,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -27499,7 +27499,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -27537,7 +27537,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -27575,7 +27575,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -27613,7 +27613,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -27651,7 +27651,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -27689,7 +27689,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -27727,7 +27727,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -27765,7 +27765,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -27803,7 +27803,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -27841,7 +27841,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -27879,7 +27879,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -27917,7 +27917,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -27955,7 +27955,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -27993,7 +27993,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -28031,7 +28031,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -28107,7 +28107,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -28145,7 +28145,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -28183,7 +28183,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -28221,7 +28221,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -28259,7 +28259,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -28297,7 +28297,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -28373,7 +28373,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -28411,7 +28411,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -28449,7 +28449,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -28487,7 +28487,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -28525,7 +28525,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -28563,7 +28563,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -28601,7 +28601,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -28639,7 +28639,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -28677,7 +28677,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -28715,7 +28715,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -28753,7 +28753,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -28791,7 +28791,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -28829,7 +28829,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -28867,7 +28867,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -28905,7 +28905,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -28981,7 +28981,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -29019,7 +29019,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -29057,7 +29057,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -29095,7 +29095,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -29133,7 +29133,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -29171,7 +29171,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:40</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -29209,7 +29209,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -29247,7 +29247,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -29285,7 +29285,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -29323,7 +29323,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -29361,7 +29361,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -29399,7 +29399,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -29437,7 +29437,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -29475,7 +29475,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -29513,7 +29513,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -29551,7 +29551,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -29627,7 +29627,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -29665,7 +29665,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -29703,7 +29703,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -29741,7 +29741,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -29779,7 +29779,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -29855,7 +29855,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -29893,7 +29893,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -29931,7 +29931,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -29969,7 +29969,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -30007,7 +30007,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -30045,7 +30045,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -30083,7 +30083,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -30121,7 +30121,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -30159,7 +30159,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -30197,7 +30197,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -30235,7 +30235,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -30273,7 +30273,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -30311,7 +30311,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -30349,7 +30349,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -30425,7 +30425,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -30463,7 +30463,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -30501,7 +30501,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -30539,7 +30539,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -30577,7 +30577,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -30615,7 +30615,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -30653,7 +30653,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -30729,7 +30729,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -30767,7 +30767,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -30805,7 +30805,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -30843,7 +30843,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -30881,7 +30881,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -30919,7 +30919,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -30957,7 +30957,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -30995,7 +30995,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -31033,7 +31033,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -31071,7 +31071,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -31109,7 +31109,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -31147,7 +31147,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -31185,7 +31185,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -31223,7 +31223,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -31261,7 +31261,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -31299,7 +31299,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -31337,7 +31337,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -31375,7 +31375,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -31413,7 +31413,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -31451,7 +31451,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -31489,7 +31489,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -31527,7 +31527,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -31603,7 +31603,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -31641,7 +31641,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -31679,7 +31679,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -31717,7 +31717,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -31755,7 +31755,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -31793,7 +31793,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -31831,7 +31831,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -31869,7 +31869,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -31907,7 +31907,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -31945,7 +31945,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -31983,7 +31983,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -32021,7 +32021,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -32059,7 +32059,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -32097,7 +32097,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -32135,7 +32135,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -32173,7 +32173,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -32211,7 +32211,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -32249,7 +32249,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -32325,7 +32325,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -32363,7 +32363,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -32401,7 +32401,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -32477,7 +32477,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -32515,7 +32515,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -32553,7 +32553,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -32591,7 +32591,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -32629,7 +32629,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -32667,7 +32667,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -32705,7 +32705,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -32743,7 +32743,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -32819,7 +32819,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -32857,7 +32857,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -32895,7 +32895,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -32933,7 +32933,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -32971,7 +32971,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -33009,7 +33009,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -33047,7 +33047,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -33085,7 +33085,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -33123,7 +33123,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -33161,7 +33161,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -33199,7 +33199,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -33237,7 +33237,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -33275,7 +33275,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -33351,7 +33351,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -33389,7 +33389,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -33427,7 +33427,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -33465,7 +33465,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -33503,7 +33503,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -33541,7 +33541,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -33579,7 +33579,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -33617,7 +33617,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -33655,7 +33655,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -33693,7 +33693,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -33731,7 +33731,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -33769,7 +33769,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -33807,7 +33807,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -33845,7 +33845,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -33883,7 +33883,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -33921,7 +33921,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -33959,7 +33959,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -33997,7 +33997,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -34035,7 +34035,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -34073,7 +34073,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -34111,7 +34111,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -34149,7 +34149,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -34225,7 +34225,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -34263,7 +34263,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -34301,7 +34301,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -34339,7 +34339,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -34377,7 +34377,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -34415,7 +34415,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -34453,7 +34453,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -34491,7 +34491,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -34529,7 +34529,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -34567,7 +34567,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -34605,7 +34605,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -34643,7 +34643,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -34681,7 +34681,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -34719,7 +34719,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -34757,7 +34757,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -34795,7 +34795,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -34833,7 +34833,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -34871,7 +34871,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -34909,7 +34909,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -34947,7 +34947,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -34985,7 +34985,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -35023,7 +35023,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -35099,7 +35099,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -35137,7 +35137,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -35175,7 +35175,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -35213,7 +35213,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -35251,7 +35251,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -35289,7 +35289,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -35327,7 +35327,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -35365,7 +35365,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -35403,7 +35403,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -35441,7 +35441,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -35479,7 +35479,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -35517,7 +35517,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -35555,7 +35555,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -35593,7 +35593,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -35631,7 +35631,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -35669,7 +35669,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -35707,7 +35707,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -35745,7 +35745,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -35783,7 +35783,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -35821,7 +35821,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -35859,7 +35859,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -35897,7 +35897,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -35973,7 +35973,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -36011,7 +36011,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -36087,7 +36087,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -36125,7 +36125,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -36163,7 +36163,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -36201,7 +36201,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -36239,7 +36239,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -36277,7 +36277,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -36315,7 +36315,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -36353,7 +36353,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -36391,7 +36391,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -36429,7 +36429,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -36467,7 +36467,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -36505,7 +36505,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -36581,7 +36581,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -36619,7 +36619,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -36657,7 +36657,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -36695,7 +36695,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -36733,7 +36733,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -36771,7 +36771,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -36847,7 +36847,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -36885,7 +36885,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -36923,7 +36923,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -36961,7 +36961,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -36999,7 +36999,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -37037,7 +37037,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -37075,7 +37075,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -37113,7 +37113,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -37151,7 +37151,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -37189,7 +37189,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -37227,7 +37227,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -37265,7 +37265,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -37303,7 +37303,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -37341,7 +37341,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -37379,7 +37379,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -37417,7 +37417,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -37455,7 +37455,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -37493,7 +37493,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -37531,7 +37531,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -37569,7 +37569,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -37607,7 +37607,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -37645,7 +37645,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -37721,7 +37721,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -37759,7 +37759,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -37797,7 +37797,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -37835,7 +37835,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -37873,7 +37873,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -37911,7 +37911,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -37949,7 +37949,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -37987,7 +37987,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -38025,7 +38025,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -38063,7 +38063,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -38101,7 +38101,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -38139,7 +38139,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -38177,7 +38177,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -38215,7 +38215,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -38253,7 +38253,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -38291,7 +38291,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -38329,7 +38329,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -38367,7 +38367,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -38405,7 +38405,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -38443,7 +38443,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H480" s="4" t="inlineStr"/>
@@ -38481,7 +38481,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H481" s="4" t="inlineStr"/>
@@ -38519,7 +38519,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H482" s="4" t="inlineStr"/>
@@ -38557,7 +38557,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H483" s="4" t="inlineStr"/>
@@ -38595,7 +38595,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H484" s="4" t="inlineStr"/>
@@ -38633,7 +38633,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H485" s="4" t="inlineStr"/>
@@ -38671,7 +38671,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H486" s="4" t="inlineStr"/>
@@ -38709,7 +38709,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H487" s="4" t="inlineStr"/>
@@ -38747,7 +38747,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H488" s="4" t="inlineStr"/>
@@ -38785,7 +38785,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H489" s="4" t="inlineStr"/>
@@ -38823,7 +38823,7 @@
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H490" s="4" t="inlineStr"/>
@@ -38861,7 +38861,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H491" s="4" t="inlineStr"/>
@@ -38899,7 +38899,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:06</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H492" s="4" t="inlineStr"/>
@@ -38937,7 +38937,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H493" s="4" t="inlineStr"/>
@@ -38975,7 +38975,7 @@
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H494" s="4" t="inlineStr"/>
@@ -39013,7 +39013,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H495" s="4" t="inlineStr"/>
@@ -39051,7 +39051,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H496" s="4" t="inlineStr"/>
@@ -39089,7 +39089,7 @@
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H497" s="4" t="inlineStr"/>
@@ -39127,7 +39127,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H498" s="4" t="inlineStr"/>
@@ -39165,7 +39165,7 @@
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H499" s="4" t="inlineStr"/>
@@ -39203,7 +39203,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H500" s="4" t="inlineStr"/>
@@ -39241,7 +39241,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H501" s="4" t="inlineStr"/>
@@ -39279,7 +39279,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H502" s="4" t="inlineStr"/>
@@ -39317,7 +39317,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H503" s="4" t="inlineStr"/>
@@ -39355,7 +39355,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H504" s="4" t="inlineStr"/>
@@ -39393,7 +39393,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H505" s="4" t="inlineStr"/>
@@ -39431,7 +39431,7 @@
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H506" s="4" t="inlineStr"/>
@@ -39469,7 +39469,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H507" s="4" t="inlineStr"/>
@@ -39507,7 +39507,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H508" s="4" t="inlineStr"/>
@@ -39545,7 +39545,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H509" s="4" t="inlineStr"/>
@@ -39583,7 +39583,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H510" s="4" t="inlineStr"/>
@@ -39621,7 +39621,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H511" s="4" t="inlineStr"/>
@@ -39659,7 +39659,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H512" s="4" t="inlineStr"/>
@@ -39697,7 +39697,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H513" s="4" t="inlineStr"/>
@@ -39735,7 +39735,7 @@
       </c>
       <c r="G514" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H514" s="4" t="inlineStr"/>
@@ -39773,7 +39773,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H515" s="4" t="inlineStr"/>
@@ -39811,7 +39811,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H516" s="4" t="inlineStr"/>
@@ -39849,7 +39849,7 @@
       </c>
       <c r="G517" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H517" s="4" t="inlineStr"/>
@@ -39887,7 +39887,7 @@
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H518" s="4" t="inlineStr"/>
@@ -39925,7 +39925,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H519" s="4" t="inlineStr"/>
@@ -39963,7 +39963,7 @@
       </c>
       <c r="G520" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H520" s="4" t="inlineStr"/>
@@ -40001,7 +40001,7 @@
       </c>
       <c r="G521" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:07</t>
+          <t>2026-06-24 04:42:41</t>
         </is>
       </c>
       <c r="H521" s="4" t="inlineStr"/>
@@ -40272,7 +40272,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>2026-06-24 04:20:08</t>
+          <t>2026-06-24 04:42:42</t>
         </is>
       </c>
     </row>

--- a/reports/latest/android/Excel/Automation_Test_Report.xlsx
+++ b/reports/latest/android/Excel/Automation_Test_Report.xlsx
@@ -594,12 +594,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>26.84</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:38:26</t>
+          <t>2026-06-24 06:07:16</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -632,12 +632,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:38:57</t>
+          <t>2026-06-24 06:07:50</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -670,12 +670,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:39:26</t>
+          <t>2026-06-24 06:08:25</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -708,12 +708,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>59.63</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:40:00</t>
+          <t>2026-06-24 06:09:00</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -746,12 +746,12 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>33.30</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:41:01</t>
+          <t>2026-06-24 06:09:33</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -784,12 +784,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>29.56</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:41:30</t>
+          <t>2026-06-24 06:10:06</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -822,12 +822,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>36.93</t>
+          <t>39.58</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:07</t>
+          <t>2026-06-24 06:10:46</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -860,12 +860,12 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>33.00</t>
+          <t>35.77</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -898,12 +898,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -941,7 +941,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -979,7 +979,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -6223,7 +6223,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -7477,7 +7477,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -7553,7 +7553,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -7667,7 +7667,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -8427,7 +8427,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -8465,7 +8465,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -9073,7 +9073,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -9567,7 +9567,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -9795,7 +9795,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -9947,7 +9947,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -9985,7 +9985,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -10023,7 +10023,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -10061,7 +10061,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -10099,7 +10099,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -10213,7 +10213,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -10251,7 +10251,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -10441,7 +10441,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -10517,7 +10517,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -10555,7 +10555,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -10593,7 +10593,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -10669,7 +10669,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -10783,7 +10783,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -10897,7 +10897,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -10935,7 +10935,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -11011,7 +11011,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -11277,7 +11277,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -11353,7 +11353,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -11505,7 +11505,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -11543,7 +11543,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -11657,7 +11657,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -11733,7 +11733,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -11847,7 +11847,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -11923,7 +11923,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -12037,7 +12037,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -12075,7 +12075,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -12189,7 +12189,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -12227,7 +12227,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -12265,7 +12265,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -12303,7 +12303,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -12341,7 +12341,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -12531,7 +12531,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -12607,7 +12607,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -12645,7 +12645,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -12721,7 +12721,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -12911,7 +12911,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -12949,7 +12949,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -12987,7 +12987,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -13063,7 +13063,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -13101,7 +13101,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -13291,7 +13291,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -13443,7 +13443,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -13481,7 +13481,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -13519,7 +13519,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -13595,7 +13595,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -13709,7 +13709,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -13747,7 +13747,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -13785,7 +13785,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -13823,7 +13823,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -13861,7 +13861,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -14089,7 +14089,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -14127,7 +14127,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -14165,7 +14165,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -14203,7 +14203,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -14241,7 +14241,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -14431,7 +14431,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -14469,7 +14469,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -14545,7 +14545,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -14659,7 +14659,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -14697,7 +14697,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -14735,7 +14735,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -14773,7 +14773,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -14811,7 +14811,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -14849,7 +14849,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -14887,7 +14887,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -14925,7 +14925,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -14963,7 +14963,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -15001,7 +15001,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -15039,7 +15039,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -15153,7 +15153,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -15191,7 +15191,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -15267,7 +15267,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -15305,7 +15305,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -15381,7 +15381,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -15419,7 +15419,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -15457,7 +15457,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -15495,7 +15495,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -15571,7 +15571,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -15609,7 +15609,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -15685,7 +15685,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -15723,7 +15723,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -15799,7 +15799,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -15837,7 +15837,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -15875,7 +15875,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -15951,7 +15951,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -15989,7 +15989,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -16065,7 +16065,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -16103,7 +16103,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -16141,7 +16141,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -16179,7 +16179,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -16217,7 +16217,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -16255,7 +16255,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -16293,7 +16293,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -16407,7 +16407,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -16483,7 +16483,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -16521,7 +16521,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -16597,7 +16597,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -16673,7 +16673,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -16711,7 +16711,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -16749,7 +16749,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -16825,7 +16825,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -16863,7 +16863,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -16939,7 +16939,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -16977,7 +16977,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -17053,7 +17053,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -17091,7 +17091,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -17129,7 +17129,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -17167,7 +17167,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -17205,7 +17205,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -17243,7 +17243,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -17319,7 +17319,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -17357,7 +17357,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -17433,7 +17433,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -17471,7 +17471,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -17509,7 +17509,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -17547,7 +17547,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -17585,7 +17585,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -17737,7 +17737,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -17775,7 +17775,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -17813,7 +17813,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -17851,7 +17851,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -17965,7 +17965,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -18003,7 +18003,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -18079,7 +18079,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -18117,7 +18117,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -18155,7 +18155,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -18231,7 +18231,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -18269,7 +18269,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -18307,7 +18307,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -18345,7 +18345,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -18383,7 +18383,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -18421,7 +18421,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -18459,7 +18459,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -18497,7 +18497,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -18535,7 +18535,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -18573,7 +18573,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -18611,7 +18611,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -18649,7 +18649,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -18687,7 +18687,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H480" s="4" t="inlineStr"/>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H481" s="4" t="inlineStr"/>
@@ -18763,7 +18763,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H482" s="4" t="inlineStr"/>
@@ -18801,7 +18801,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H483" s="4" t="inlineStr"/>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H484" s="4" t="inlineStr"/>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H485" s="4" t="inlineStr"/>
@@ -18915,7 +18915,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H486" s="4" t="inlineStr"/>
@@ -18953,7 +18953,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H487" s="4" t="inlineStr"/>
@@ -18991,7 +18991,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H488" s="4" t="inlineStr"/>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H489" s="4" t="inlineStr"/>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H490" s="4" t="inlineStr"/>
@@ -19105,7 +19105,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H491" s="4" t="inlineStr"/>
@@ -19143,7 +19143,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H492" s="4" t="inlineStr"/>
@@ -19181,7 +19181,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H493" s="4" t="inlineStr"/>
@@ -19219,7 +19219,7 @@
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H494" s="4" t="inlineStr"/>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H495" s="4" t="inlineStr"/>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H496" s="4" t="inlineStr"/>
@@ -19333,7 +19333,7 @@
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H497" s="4" t="inlineStr"/>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H498" s="4" t="inlineStr"/>
@@ -19409,7 +19409,7 @@
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H499" s="4" t="inlineStr"/>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H500" s="4" t="inlineStr"/>
@@ -19485,7 +19485,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H501" s="4" t="inlineStr"/>
@@ -19523,7 +19523,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H502" s="4" t="inlineStr"/>
@@ -19561,7 +19561,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H503" s="4" t="inlineStr"/>
@@ -19599,7 +19599,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H504" s="4" t="inlineStr"/>
@@ -19637,7 +19637,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H505" s="4" t="inlineStr"/>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H506" s="4" t="inlineStr"/>
@@ -19713,7 +19713,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H507" s="4" t="inlineStr"/>
@@ -19751,7 +19751,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H508" s="4" t="inlineStr"/>
@@ -19789,7 +19789,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H509" s="4" t="inlineStr"/>
@@ -19827,7 +19827,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H510" s="4" t="inlineStr"/>
@@ -19865,7 +19865,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H511" s="4" t="inlineStr"/>
@@ -19903,7 +19903,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H512" s="4" t="inlineStr"/>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H513" s="4" t="inlineStr"/>
@@ -19979,7 +19979,7 @@
       </c>
       <c r="G514" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H514" s="4" t="inlineStr"/>
@@ -20017,7 +20017,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H515" s="4" t="inlineStr"/>
@@ -20055,7 +20055,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H516" s="4" t="inlineStr"/>
@@ -20093,7 +20093,7 @@
       </c>
       <c r="G517" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H517" s="4" t="inlineStr"/>
@@ -20131,7 +20131,7 @@
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H518" s="4" t="inlineStr"/>
@@ -20169,7 +20169,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H519" s="4" t="inlineStr"/>
@@ -20207,7 +20207,7 @@
       </c>
       <c r="G520" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H520" s="4" t="inlineStr"/>
@@ -20245,7 +20245,7 @@
       </c>
       <c r="G521" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H521" s="4" t="inlineStr"/>
@@ -20350,12 +20350,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>26.84</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:38:26</t>
+          <t>2026-06-24 06:07:16</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -20388,12 +20388,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:38:57</t>
+          <t>2026-06-24 06:07:50</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -20426,12 +20426,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:39:26</t>
+          <t>2026-06-24 06:08:25</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -20464,12 +20464,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>59.63</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:40:00</t>
+          <t>2026-06-24 06:09:00</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -20502,12 +20502,12 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>33.30</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:41:01</t>
+          <t>2026-06-24 06:09:33</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -20540,12 +20540,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>29.56</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:41:30</t>
+          <t>2026-06-24 06:10:06</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -20578,12 +20578,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>36.93</t>
+          <t>39.58</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:07</t>
+          <t>2026-06-24 06:10:46</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -20616,12 +20616,12 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>33.00</t>
+          <t>35.77</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -20654,12 +20654,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -20697,7 +20697,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -20735,7 +20735,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -20773,7 +20773,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -20811,7 +20811,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -20849,7 +20849,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -20887,7 +20887,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -20925,7 +20925,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -20963,7 +20963,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -21001,7 +21001,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -21039,7 +21039,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -21115,7 +21115,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -21153,7 +21153,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -21191,7 +21191,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -21229,7 +21229,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -21267,7 +21267,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -21305,7 +21305,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -21343,7 +21343,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -21419,7 +21419,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -21495,7 +21495,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -21533,7 +21533,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -21571,7 +21571,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -21647,7 +21647,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -21685,7 +21685,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -21723,7 +21723,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -21761,7 +21761,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -21875,7 +21875,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -21913,7 +21913,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -21951,7 +21951,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -21989,7 +21989,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -22027,7 +22027,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -22065,7 +22065,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -22103,7 +22103,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -22141,7 +22141,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -22179,7 +22179,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -22217,7 +22217,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -22255,7 +22255,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -22293,7 +22293,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -22331,7 +22331,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -22369,7 +22369,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -22407,7 +22407,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -22445,7 +22445,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -22521,7 +22521,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -22559,7 +22559,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -22597,7 +22597,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -22635,7 +22635,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -22711,7 +22711,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -22749,7 +22749,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -22787,7 +22787,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -22825,7 +22825,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -22901,7 +22901,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -22939,7 +22939,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -22977,7 +22977,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -23015,7 +23015,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -23053,7 +23053,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -23091,7 +23091,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -23167,7 +23167,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -23205,7 +23205,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -23243,7 +23243,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -23281,7 +23281,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -23319,7 +23319,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -23357,7 +23357,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -23395,7 +23395,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -23433,7 +23433,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -23509,7 +23509,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -23547,7 +23547,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -23585,7 +23585,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -23623,7 +23623,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -23661,7 +23661,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -23699,7 +23699,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -23737,7 +23737,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -23775,7 +23775,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -23813,7 +23813,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -23851,7 +23851,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -23889,7 +23889,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -23927,7 +23927,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -23965,7 +23965,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -24003,7 +24003,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -24041,7 +24041,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -24079,7 +24079,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -24117,7 +24117,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -24193,7 +24193,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -24231,7 +24231,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -24307,7 +24307,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -24345,7 +24345,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -24383,7 +24383,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -24421,7 +24421,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -24459,7 +24459,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -24497,7 +24497,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -24535,7 +24535,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -24573,7 +24573,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -24611,7 +24611,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -24649,7 +24649,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -24687,7 +24687,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -24725,7 +24725,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -24763,7 +24763,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -24801,7 +24801,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -24839,7 +24839,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -24877,7 +24877,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -24915,7 +24915,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -24953,7 +24953,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -24991,7 +24991,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -25029,7 +25029,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -25067,7 +25067,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -25105,7 +25105,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -25143,7 +25143,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -25219,7 +25219,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -25257,7 +25257,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -25295,7 +25295,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -25333,7 +25333,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -25371,7 +25371,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -25409,7 +25409,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -25447,7 +25447,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -25485,7 +25485,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -25523,7 +25523,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -25561,7 +25561,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -25599,7 +25599,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -25637,7 +25637,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -25675,7 +25675,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -25713,7 +25713,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -25751,7 +25751,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -25789,7 +25789,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -25827,7 +25827,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -25865,7 +25865,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -25903,7 +25903,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -25941,7 +25941,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -25979,7 +25979,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -26017,7 +26017,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -26055,7 +26055,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -26093,7 +26093,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -26169,7 +26169,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -26207,7 +26207,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -26245,7 +26245,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -26359,7 +26359,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -26397,7 +26397,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -26435,7 +26435,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -26473,7 +26473,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -26511,7 +26511,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -26549,7 +26549,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -26587,7 +26587,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -26625,7 +26625,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -26663,7 +26663,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -26701,7 +26701,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -26739,7 +26739,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -26815,7 +26815,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -26853,7 +26853,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -26891,7 +26891,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -26929,7 +26929,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -26967,7 +26967,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -27005,7 +27005,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -27043,7 +27043,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -27081,7 +27081,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -27119,7 +27119,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -27157,7 +27157,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -27233,7 +27233,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -27271,7 +27271,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -27309,7 +27309,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -27347,7 +27347,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -27385,7 +27385,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -27423,7 +27423,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -27461,7 +27461,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -27499,7 +27499,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -27537,7 +27537,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -27575,7 +27575,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -27613,7 +27613,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -27651,7 +27651,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -27689,7 +27689,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -27727,7 +27727,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -27765,7 +27765,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -27803,7 +27803,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -27841,7 +27841,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -27879,7 +27879,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -27917,7 +27917,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -27955,7 +27955,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -27993,7 +27993,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -28031,7 +28031,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -28107,7 +28107,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -28145,7 +28145,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -28183,7 +28183,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -28221,7 +28221,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -28259,7 +28259,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -28297,7 +28297,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -28373,7 +28373,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -28411,7 +28411,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -28449,7 +28449,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -28487,7 +28487,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -28525,7 +28525,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -28563,7 +28563,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -28601,7 +28601,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -28639,7 +28639,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -28677,7 +28677,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -28715,7 +28715,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -28753,7 +28753,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -28791,7 +28791,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -28829,7 +28829,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -28867,7 +28867,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -28905,7 +28905,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -28981,7 +28981,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -29019,7 +29019,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -29057,7 +29057,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -29095,7 +29095,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -29133,7 +29133,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -29171,7 +29171,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:40</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -29209,7 +29209,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -29247,7 +29247,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -29285,7 +29285,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -29323,7 +29323,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -29361,7 +29361,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -29399,7 +29399,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -29437,7 +29437,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -29475,7 +29475,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -29513,7 +29513,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -29551,7 +29551,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -29627,7 +29627,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -29665,7 +29665,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -29703,7 +29703,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -29741,7 +29741,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -29779,7 +29779,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -29855,7 +29855,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -29893,7 +29893,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -29931,7 +29931,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -29969,7 +29969,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -30007,7 +30007,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -30045,7 +30045,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -30083,7 +30083,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -30121,7 +30121,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -30159,7 +30159,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -30197,7 +30197,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -30235,7 +30235,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -30273,7 +30273,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -30311,7 +30311,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -30349,7 +30349,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -30425,7 +30425,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -30463,7 +30463,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -30501,7 +30501,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -30539,7 +30539,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -30577,7 +30577,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -30615,7 +30615,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -30653,7 +30653,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -30729,7 +30729,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -30767,7 +30767,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -30805,7 +30805,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -30843,7 +30843,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -30881,7 +30881,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -30919,7 +30919,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -30957,7 +30957,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -30995,7 +30995,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -31033,7 +31033,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -31071,7 +31071,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -31109,7 +31109,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -31147,7 +31147,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -31185,7 +31185,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -31223,7 +31223,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -31261,7 +31261,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -31299,7 +31299,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -31337,7 +31337,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -31375,7 +31375,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -31413,7 +31413,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -31451,7 +31451,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -31489,7 +31489,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -31527,7 +31527,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -31603,7 +31603,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -31641,7 +31641,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -31679,7 +31679,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -31717,7 +31717,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -31755,7 +31755,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -31793,7 +31793,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -31831,7 +31831,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -31869,7 +31869,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -31907,7 +31907,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -31945,7 +31945,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -31983,7 +31983,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -32021,7 +32021,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -32059,7 +32059,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -32097,7 +32097,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -32135,7 +32135,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -32173,7 +32173,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -32211,7 +32211,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -32249,7 +32249,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -32325,7 +32325,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -32363,7 +32363,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -32401,7 +32401,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -32477,7 +32477,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -32515,7 +32515,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -32553,7 +32553,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -32591,7 +32591,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -32629,7 +32629,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -32667,7 +32667,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -32705,7 +32705,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -32743,7 +32743,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -32819,7 +32819,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -32857,7 +32857,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -32895,7 +32895,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -32933,7 +32933,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -32971,7 +32971,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -33009,7 +33009,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -33047,7 +33047,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -33085,7 +33085,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -33123,7 +33123,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -33161,7 +33161,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -33199,7 +33199,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -33237,7 +33237,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -33275,7 +33275,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -33351,7 +33351,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -33389,7 +33389,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -33427,7 +33427,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -33465,7 +33465,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -33503,7 +33503,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -33541,7 +33541,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -33579,7 +33579,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -33617,7 +33617,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -33655,7 +33655,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -33693,7 +33693,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -33731,7 +33731,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -33769,7 +33769,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -33807,7 +33807,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -33845,7 +33845,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -33883,7 +33883,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -33921,7 +33921,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -33959,7 +33959,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -33997,7 +33997,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -34035,7 +34035,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -34073,7 +34073,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -34111,7 +34111,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -34149,7 +34149,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -34225,7 +34225,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -34263,7 +34263,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -34301,7 +34301,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -34339,7 +34339,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -34377,7 +34377,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -34415,7 +34415,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -34453,7 +34453,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -34491,7 +34491,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -34529,7 +34529,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -34567,7 +34567,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -34605,7 +34605,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -34643,7 +34643,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -34681,7 +34681,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -34719,7 +34719,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -34757,7 +34757,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -34795,7 +34795,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -34833,7 +34833,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -34871,7 +34871,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -34909,7 +34909,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -34947,7 +34947,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -34985,7 +34985,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -35023,7 +35023,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -35099,7 +35099,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -35137,7 +35137,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -35175,7 +35175,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -35213,7 +35213,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -35251,7 +35251,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -35289,7 +35289,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -35327,7 +35327,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -35365,7 +35365,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -35403,7 +35403,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -35441,7 +35441,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -35479,7 +35479,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -35517,7 +35517,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -35555,7 +35555,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -35593,7 +35593,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -35631,7 +35631,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -35669,7 +35669,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -35707,7 +35707,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -35745,7 +35745,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -35783,7 +35783,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -35821,7 +35821,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -35859,7 +35859,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -35897,7 +35897,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -35973,7 +35973,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -36011,7 +36011,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -36087,7 +36087,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -36125,7 +36125,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -36163,7 +36163,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -36201,7 +36201,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -36239,7 +36239,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -36277,7 +36277,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -36315,7 +36315,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -36353,7 +36353,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -36391,7 +36391,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -36429,7 +36429,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -36467,7 +36467,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -36505,7 +36505,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -36581,7 +36581,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -36619,7 +36619,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -36657,7 +36657,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -36695,7 +36695,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -36733,7 +36733,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -36771,7 +36771,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -36847,7 +36847,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -36885,7 +36885,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -36923,7 +36923,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -36961,7 +36961,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -36999,7 +36999,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -37037,7 +37037,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -37075,7 +37075,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -37113,7 +37113,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -37151,7 +37151,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -37189,7 +37189,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -37227,7 +37227,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -37265,7 +37265,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -37303,7 +37303,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -37341,7 +37341,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -37379,7 +37379,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -37417,7 +37417,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -37455,7 +37455,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -37493,7 +37493,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -37531,7 +37531,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -37569,7 +37569,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -37607,7 +37607,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -37645,7 +37645,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -37721,7 +37721,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -37759,7 +37759,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -37797,7 +37797,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -37835,7 +37835,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -37873,7 +37873,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -37911,7 +37911,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -37949,7 +37949,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -37987,7 +37987,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -38025,7 +38025,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -38063,7 +38063,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -38101,7 +38101,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -38139,7 +38139,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -38177,7 +38177,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -38215,7 +38215,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -38253,7 +38253,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -38291,7 +38291,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -38329,7 +38329,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -38367,7 +38367,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -38405,7 +38405,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -38443,7 +38443,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H480" s="4" t="inlineStr"/>
@@ -38481,7 +38481,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H481" s="4" t="inlineStr"/>
@@ -38519,7 +38519,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H482" s="4" t="inlineStr"/>
@@ -38557,7 +38557,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H483" s="4" t="inlineStr"/>
@@ -38595,7 +38595,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H484" s="4" t="inlineStr"/>
@@ -38633,7 +38633,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H485" s="4" t="inlineStr"/>
@@ -38671,7 +38671,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H486" s="4" t="inlineStr"/>
@@ -38709,7 +38709,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H487" s="4" t="inlineStr"/>
@@ -38747,7 +38747,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H488" s="4" t="inlineStr"/>
@@ -38785,7 +38785,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H489" s="4" t="inlineStr"/>
@@ -38823,7 +38823,7 @@
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H490" s="4" t="inlineStr"/>
@@ -38861,7 +38861,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H491" s="4" t="inlineStr"/>
@@ -38899,7 +38899,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H492" s="4" t="inlineStr"/>
@@ -38937,7 +38937,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H493" s="4" t="inlineStr"/>
@@ -38975,7 +38975,7 @@
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H494" s="4" t="inlineStr"/>
@@ -39013,7 +39013,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H495" s="4" t="inlineStr"/>
@@ -39051,7 +39051,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H496" s="4" t="inlineStr"/>
@@ -39089,7 +39089,7 @@
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H497" s="4" t="inlineStr"/>
@@ -39127,7 +39127,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H498" s="4" t="inlineStr"/>
@@ -39165,7 +39165,7 @@
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H499" s="4" t="inlineStr"/>
@@ -39203,7 +39203,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H500" s="4" t="inlineStr"/>
@@ -39241,7 +39241,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H501" s="4" t="inlineStr"/>
@@ -39279,7 +39279,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H502" s="4" t="inlineStr"/>
@@ -39317,7 +39317,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H503" s="4" t="inlineStr"/>
@@ -39355,7 +39355,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H504" s="4" t="inlineStr"/>
@@ -39393,7 +39393,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H505" s="4" t="inlineStr"/>
@@ -39431,7 +39431,7 @@
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H506" s="4" t="inlineStr"/>
@@ -39469,7 +39469,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H507" s="4" t="inlineStr"/>
@@ -39507,7 +39507,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H508" s="4" t="inlineStr"/>
@@ -39545,7 +39545,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H509" s="4" t="inlineStr"/>
@@ -39583,7 +39583,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H510" s="4" t="inlineStr"/>
@@ -39621,7 +39621,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H511" s="4" t="inlineStr"/>
@@ -39659,7 +39659,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H512" s="4" t="inlineStr"/>
@@ -39697,7 +39697,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H513" s="4" t="inlineStr"/>
@@ -39735,7 +39735,7 @@
       </c>
       <c r="G514" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H514" s="4" t="inlineStr"/>
@@ -39773,7 +39773,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H515" s="4" t="inlineStr"/>
@@ -39811,7 +39811,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H516" s="4" t="inlineStr"/>
@@ -39849,7 +39849,7 @@
       </c>
       <c r="G517" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H517" s="4" t="inlineStr"/>
@@ -39887,7 +39887,7 @@
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H518" s="4" t="inlineStr"/>
@@ -39925,7 +39925,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H519" s="4" t="inlineStr"/>
@@ -39963,7 +39963,7 @@
       </c>
       <c r="G520" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H520" s="4" t="inlineStr"/>
@@ -40001,7 +40001,7 @@
       </c>
       <c r="G521" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:41</t>
+          <t>2026-06-24 06:11:22</t>
         </is>
       </c>
       <c r="H521" s="4" t="inlineStr"/>
@@ -40272,7 +40272,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>2026-06-24 04:42:42</t>
+          <t>2026-06-24 06:11:24</t>
         </is>
       </c>
     </row>

--- a/reports/latest/android/Excel/Automation_Test_Report.xlsx
+++ b/reports/latest/android/Excel/Automation_Test_Report.xlsx
@@ -594,12 +594,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>26.84</t>
+          <t>24.02</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:07:16</t>
+          <t>2026-06-24 06:43:35</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -632,12 +632,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>33.40</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:07:50</t>
+          <t>2026-06-24 06:44:08</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -670,12 +670,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>31.97</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:08:25</t>
+          <t>2026-06-24 06:44:40</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -708,12 +708,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>33.52</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:09:00</t>
+          <t>2026-06-24 06:45:14</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -746,12 +746,12 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>33.30</t>
+          <t>31.89</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:09:33</t>
+          <t>2026-06-24 06:45:46</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -784,12 +784,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:10:06</t>
+          <t>2026-06-24 06:46:18</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -822,12 +822,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:10:46</t>
+          <t>2026-06-24 06:46:57</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -860,12 +860,12 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -898,12 +898,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -941,7 +941,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -979,7 +979,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -6223,7 +6223,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -7477,7 +7477,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -7553,7 +7553,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -7667,7 +7667,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -8427,7 +8427,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -8465,7 +8465,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -9073,7 +9073,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -9567,7 +9567,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -9795,7 +9795,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -9947,7 +9947,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -9985,7 +9985,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -10023,7 +10023,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -10061,7 +10061,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -10099,7 +10099,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -10213,7 +10213,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -10251,7 +10251,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -10441,7 +10441,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -10517,7 +10517,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -10555,7 +10555,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -10593,7 +10593,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -10669,7 +10669,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -10783,7 +10783,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -10897,7 +10897,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -10935,7 +10935,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -11011,7 +11011,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -11277,7 +11277,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -11353,7 +11353,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -11505,7 +11505,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -11543,7 +11543,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -11657,7 +11657,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -11733,7 +11733,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -11847,7 +11847,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -11923,7 +11923,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -12037,7 +12037,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -12075,7 +12075,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -12189,7 +12189,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -12227,7 +12227,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -12265,7 +12265,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -12303,7 +12303,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -12341,7 +12341,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -12531,7 +12531,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -12607,7 +12607,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -12645,7 +12645,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -12721,7 +12721,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -12911,7 +12911,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -12949,7 +12949,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -12987,7 +12987,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -13063,7 +13063,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -13101,7 +13101,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -13291,7 +13291,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -13443,7 +13443,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -13481,7 +13481,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -13519,7 +13519,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -13595,7 +13595,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -13709,7 +13709,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -13747,7 +13747,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -13785,7 +13785,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -13823,7 +13823,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -13861,7 +13861,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -14089,7 +14089,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -14127,7 +14127,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -14165,7 +14165,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -14203,7 +14203,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -14241,7 +14241,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -14431,7 +14431,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -14469,7 +14469,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -14545,7 +14545,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -14659,7 +14659,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -14697,7 +14697,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -14735,7 +14735,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -14773,7 +14773,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -14811,7 +14811,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -14849,7 +14849,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -14887,7 +14887,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -14925,7 +14925,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -14963,7 +14963,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -15001,7 +15001,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -15039,7 +15039,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -15153,7 +15153,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -15191,7 +15191,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -15267,7 +15267,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -15305,7 +15305,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -15381,7 +15381,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -15419,7 +15419,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -15457,7 +15457,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -15495,7 +15495,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -15571,7 +15571,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -15609,7 +15609,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -15685,7 +15685,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -15723,7 +15723,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -15799,7 +15799,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -15837,7 +15837,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -15875,7 +15875,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -15951,7 +15951,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -15989,7 +15989,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -16065,7 +16065,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -16103,7 +16103,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -16141,7 +16141,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -16179,7 +16179,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -16217,7 +16217,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -16255,7 +16255,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -16293,7 +16293,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -16407,7 +16407,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -16483,7 +16483,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -16521,7 +16521,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -16597,7 +16597,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -16673,7 +16673,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -16711,7 +16711,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -16749,7 +16749,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -16825,7 +16825,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -16863,7 +16863,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -16939,7 +16939,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -16977,7 +16977,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -17053,7 +17053,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -17091,7 +17091,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -17129,7 +17129,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -17167,7 +17167,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -17205,7 +17205,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -17243,7 +17243,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -17319,7 +17319,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -17357,7 +17357,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -17433,7 +17433,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -17471,7 +17471,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -17509,7 +17509,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -17547,7 +17547,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -17585,7 +17585,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -17737,7 +17737,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -17775,7 +17775,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -17813,7 +17813,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -17851,7 +17851,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -17965,7 +17965,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -18003,7 +18003,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -18079,7 +18079,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -18117,7 +18117,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -18155,7 +18155,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -18231,7 +18231,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -18269,7 +18269,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -18307,7 +18307,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -18345,7 +18345,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -18383,7 +18383,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -18421,7 +18421,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -18459,7 +18459,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -18497,7 +18497,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -18535,7 +18535,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -18573,7 +18573,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -18611,7 +18611,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -18649,7 +18649,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -18687,7 +18687,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H480" s="4" t="inlineStr"/>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H481" s="4" t="inlineStr"/>
@@ -18763,7 +18763,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H482" s="4" t="inlineStr"/>
@@ -18801,7 +18801,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H483" s="4" t="inlineStr"/>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H484" s="4" t="inlineStr"/>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H485" s="4" t="inlineStr"/>
@@ -18915,7 +18915,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H486" s="4" t="inlineStr"/>
@@ -18953,7 +18953,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H487" s="4" t="inlineStr"/>
@@ -18991,7 +18991,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H488" s="4" t="inlineStr"/>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H489" s="4" t="inlineStr"/>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H490" s="4" t="inlineStr"/>
@@ -19105,7 +19105,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H491" s="4" t="inlineStr"/>
@@ -19143,7 +19143,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H492" s="4" t="inlineStr"/>
@@ -19181,7 +19181,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H493" s="4" t="inlineStr"/>
@@ -19219,7 +19219,7 @@
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H494" s="4" t="inlineStr"/>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H495" s="4" t="inlineStr"/>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H496" s="4" t="inlineStr"/>
@@ -19333,7 +19333,7 @@
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H497" s="4" t="inlineStr"/>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H498" s="4" t="inlineStr"/>
@@ -19409,7 +19409,7 @@
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H499" s="4" t="inlineStr"/>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H500" s="4" t="inlineStr"/>
@@ -19485,7 +19485,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H501" s="4" t="inlineStr"/>
@@ -19523,7 +19523,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H502" s="4" t="inlineStr"/>
@@ -19561,7 +19561,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H503" s="4" t="inlineStr"/>
@@ -19599,7 +19599,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H504" s="4" t="inlineStr"/>
@@ -19637,7 +19637,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H505" s="4" t="inlineStr"/>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H506" s="4" t="inlineStr"/>
@@ -19713,7 +19713,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H507" s="4" t="inlineStr"/>
@@ -19751,7 +19751,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H508" s="4" t="inlineStr"/>
@@ -19789,7 +19789,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H509" s="4" t="inlineStr"/>
@@ -19827,7 +19827,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H510" s="4" t="inlineStr"/>
@@ -19865,7 +19865,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H511" s="4" t="inlineStr"/>
@@ -19903,7 +19903,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H512" s="4" t="inlineStr"/>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H513" s="4" t="inlineStr"/>
@@ -19979,7 +19979,7 @@
       </c>
       <c r="G514" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H514" s="4" t="inlineStr"/>
@@ -20017,7 +20017,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H515" s="4" t="inlineStr"/>
@@ -20055,7 +20055,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H516" s="4" t="inlineStr"/>
@@ -20093,7 +20093,7 @@
       </c>
       <c r="G517" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H517" s="4" t="inlineStr"/>
@@ -20131,7 +20131,7 @@
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H518" s="4" t="inlineStr"/>
@@ -20169,7 +20169,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H519" s="4" t="inlineStr"/>
@@ -20207,7 +20207,7 @@
       </c>
       <c r="G520" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H520" s="4" t="inlineStr"/>
@@ -20245,7 +20245,7 @@
       </c>
       <c r="G521" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H521" s="4" t="inlineStr"/>
@@ -20350,12 +20350,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>26.84</t>
+          <t>24.02</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:07:16</t>
+          <t>2026-06-24 06:43:35</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -20388,12 +20388,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>33.40</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:07:50</t>
+          <t>2026-06-24 06:44:08</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -20426,12 +20426,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>31.97</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:08:25</t>
+          <t>2026-06-24 06:44:40</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -20464,12 +20464,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>33.52</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:09:00</t>
+          <t>2026-06-24 06:45:14</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -20502,12 +20502,12 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>33.30</t>
+          <t>31.89</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:09:33</t>
+          <t>2026-06-24 06:45:46</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -20540,12 +20540,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:10:06</t>
+          <t>2026-06-24 06:46:18</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -20578,12 +20578,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:10:46</t>
+          <t>2026-06-24 06:46:57</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -20616,12 +20616,12 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -20654,12 +20654,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -20697,7 +20697,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -20735,7 +20735,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -20773,7 +20773,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -20811,7 +20811,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -20849,7 +20849,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -20887,7 +20887,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -20925,7 +20925,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -20963,7 +20963,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -21001,7 +21001,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -21039,7 +21039,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -21115,7 +21115,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -21153,7 +21153,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -21191,7 +21191,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -21229,7 +21229,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -21267,7 +21267,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -21305,7 +21305,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -21343,7 +21343,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -21419,7 +21419,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -21495,7 +21495,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -21533,7 +21533,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -21571,7 +21571,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -21647,7 +21647,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -21685,7 +21685,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -21723,7 +21723,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -21761,7 +21761,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -21875,7 +21875,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -21913,7 +21913,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -21951,7 +21951,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -21989,7 +21989,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -22027,7 +22027,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -22065,7 +22065,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -22103,7 +22103,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -22141,7 +22141,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -22179,7 +22179,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -22217,7 +22217,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -22255,7 +22255,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -22293,7 +22293,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -22331,7 +22331,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -22369,7 +22369,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -22407,7 +22407,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -22445,7 +22445,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -22521,7 +22521,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -22559,7 +22559,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -22597,7 +22597,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -22635,7 +22635,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -22711,7 +22711,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -22749,7 +22749,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -22787,7 +22787,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -22825,7 +22825,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -22901,7 +22901,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -22939,7 +22939,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -22977,7 +22977,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -23015,7 +23015,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -23053,7 +23053,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -23091,7 +23091,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -23167,7 +23167,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -23205,7 +23205,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -23243,7 +23243,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -23281,7 +23281,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -23319,7 +23319,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -23357,7 +23357,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -23395,7 +23395,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -23433,7 +23433,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -23509,7 +23509,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -23547,7 +23547,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -23585,7 +23585,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -23623,7 +23623,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -23661,7 +23661,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -23699,7 +23699,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -23737,7 +23737,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -23775,7 +23775,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -23813,7 +23813,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -23851,7 +23851,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -23889,7 +23889,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -23927,7 +23927,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -23965,7 +23965,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -24003,7 +24003,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -24041,7 +24041,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -24079,7 +24079,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -24117,7 +24117,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -24193,7 +24193,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -24231,7 +24231,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -24307,7 +24307,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -24345,7 +24345,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -24383,7 +24383,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -24421,7 +24421,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -24459,7 +24459,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -24497,7 +24497,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -24535,7 +24535,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -24573,7 +24573,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -24611,7 +24611,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -24649,7 +24649,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -24687,7 +24687,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -24725,7 +24725,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -24763,7 +24763,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -24801,7 +24801,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -24839,7 +24839,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -24877,7 +24877,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -24915,7 +24915,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -24953,7 +24953,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -24991,7 +24991,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -25029,7 +25029,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -25067,7 +25067,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -25105,7 +25105,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -25143,7 +25143,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -25219,7 +25219,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -25257,7 +25257,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -25295,7 +25295,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -25333,7 +25333,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -25371,7 +25371,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -25409,7 +25409,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -25447,7 +25447,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -25485,7 +25485,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -25523,7 +25523,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -25561,7 +25561,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -25599,7 +25599,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -25637,7 +25637,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -25675,7 +25675,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -25713,7 +25713,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -25751,7 +25751,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -25789,7 +25789,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -25827,7 +25827,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -25865,7 +25865,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -25903,7 +25903,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -25941,7 +25941,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -25979,7 +25979,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -26017,7 +26017,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -26055,7 +26055,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -26093,7 +26093,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -26169,7 +26169,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -26207,7 +26207,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -26245,7 +26245,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -26359,7 +26359,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -26397,7 +26397,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -26435,7 +26435,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -26473,7 +26473,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -26511,7 +26511,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -26549,7 +26549,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -26587,7 +26587,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -26625,7 +26625,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -26663,7 +26663,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -26701,7 +26701,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -26739,7 +26739,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -26815,7 +26815,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -26853,7 +26853,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -26891,7 +26891,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -26929,7 +26929,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -26967,7 +26967,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -27005,7 +27005,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -27043,7 +27043,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -27081,7 +27081,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -27119,7 +27119,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -27157,7 +27157,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -27233,7 +27233,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -27271,7 +27271,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -27309,7 +27309,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -27347,7 +27347,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -27385,7 +27385,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -27423,7 +27423,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -27461,7 +27461,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -27499,7 +27499,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -27537,7 +27537,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -27575,7 +27575,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -27613,7 +27613,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -27651,7 +27651,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -27689,7 +27689,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -27727,7 +27727,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -27765,7 +27765,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -27803,7 +27803,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -27841,7 +27841,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -27879,7 +27879,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -27917,7 +27917,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -27955,7 +27955,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -27993,7 +27993,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -28031,7 +28031,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -28107,7 +28107,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -28145,7 +28145,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -28183,7 +28183,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -28221,7 +28221,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -28259,7 +28259,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -28297,7 +28297,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -28373,7 +28373,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -28411,7 +28411,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -28449,7 +28449,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -28487,7 +28487,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -28525,7 +28525,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -28563,7 +28563,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -28601,7 +28601,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -28639,7 +28639,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -28677,7 +28677,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -28715,7 +28715,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -28753,7 +28753,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -28791,7 +28791,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -28829,7 +28829,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -28867,7 +28867,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -28905,7 +28905,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -28981,7 +28981,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -29019,7 +29019,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -29057,7 +29057,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -29095,7 +29095,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -29133,7 +29133,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -29171,7 +29171,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -29209,7 +29209,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -29247,7 +29247,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -29285,7 +29285,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -29323,7 +29323,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -29361,7 +29361,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -29399,7 +29399,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -29437,7 +29437,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -29475,7 +29475,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -29513,7 +29513,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -29551,7 +29551,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -29627,7 +29627,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -29665,7 +29665,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -29703,7 +29703,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -29741,7 +29741,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -29779,7 +29779,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -29855,7 +29855,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -29893,7 +29893,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -29931,7 +29931,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -29969,7 +29969,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -30007,7 +30007,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -30045,7 +30045,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -30083,7 +30083,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -30121,7 +30121,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -30159,7 +30159,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -30197,7 +30197,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -30235,7 +30235,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -30273,7 +30273,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -30311,7 +30311,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -30349,7 +30349,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -30425,7 +30425,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -30463,7 +30463,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -30501,7 +30501,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -30539,7 +30539,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -30577,7 +30577,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -30615,7 +30615,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -30653,7 +30653,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -30729,7 +30729,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -30767,7 +30767,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -30805,7 +30805,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -30843,7 +30843,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -30881,7 +30881,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -30919,7 +30919,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -30957,7 +30957,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -30995,7 +30995,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -31033,7 +31033,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -31071,7 +31071,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -31109,7 +31109,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -31147,7 +31147,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -31185,7 +31185,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -31223,7 +31223,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -31261,7 +31261,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -31299,7 +31299,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -31337,7 +31337,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -31375,7 +31375,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -31413,7 +31413,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -31451,7 +31451,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -31489,7 +31489,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -31527,7 +31527,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -31603,7 +31603,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -31641,7 +31641,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -31679,7 +31679,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -31717,7 +31717,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -31755,7 +31755,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -31793,7 +31793,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -31831,7 +31831,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -31869,7 +31869,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -31907,7 +31907,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -31945,7 +31945,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -31983,7 +31983,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -32021,7 +32021,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -32059,7 +32059,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -32097,7 +32097,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -32135,7 +32135,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -32173,7 +32173,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -32211,7 +32211,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -32249,7 +32249,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -32325,7 +32325,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -32363,7 +32363,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -32401,7 +32401,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -32477,7 +32477,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -32515,7 +32515,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -32553,7 +32553,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -32591,7 +32591,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -32629,7 +32629,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -32667,7 +32667,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -32705,7 +32705,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -32743,7 +32743,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -32819,7 +32819,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -32857,7 +32857,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -32895,7 +32895,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -32933,7 +32933,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -32971,7 +32971,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -33009,7 +33009,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -33047,7 +33047,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -33085,7 +33085,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -33123,7 +33123,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -33161,7 +33161,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -33199,7 +33199,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -33237,7 +33237,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -33275,7 +33275,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -33351,7 +33351,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -33389,7 +33389,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -33427,7 +33427,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -33465,7 +33465,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -33503,7 +33503,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -33541,7 +33541,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -33579,7 +33579,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -33617,7 +33617,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -33655,7 +33655,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -33693,7 +33693,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -33731,7 +33731,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -33769,7 +33769,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -33807,7 +33807,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -33845,7 +33845,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -33883,7 +33883,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -33921,7 +33921,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -33959,7 +33959,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -33997,7 +33997,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -34035,7 +34035,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -34073,7 +34073,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -34111,7 +34111,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -34149,7 +34149,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -34225,7 +34225,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -34263,7 +34263,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -34301,7 +34301,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -34339,7 +34339,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -34377,7 +34377,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -34415,7 +34415,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -34453,7 +34453,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -34491,7 +34491,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -34529,7 +34529,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -34567,7 +34567,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -34605,7 +34605,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -34643,7 +34643,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -34681,7 +34681,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -34719,7 +34719,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -34757,7 +34757,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -34795,7 +34795,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -34833,7 +34833,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -34871,7 +34871,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -34909,7 +34909,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -34947,7 +34947,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -34985,7 +34985,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -35023,7 +35023,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -35099,7 +35099,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -35137,7 +35137,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -35175,7 +35175,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -35213,7 +35213,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -35251,7 +35251,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -35289,7 +35289,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -35327,7 +35327,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -35365,7 +35365,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -35403,7 +35403,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -35441,7 +35441,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -35479,7 +35479,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -35517,7 +35517,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -35555,7 +35555,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -35593,7 +35593,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -35631,7 +35631,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -35669,7 +35669,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -35707,7 +35707,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -35745,7 +35745,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -35783,7 +35783,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -35821,7 +35821,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -35859,7 +35859,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -35897,7 +35897,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -35973,7 +35973,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -36011,7 +36011,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -36087,7 +36087,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -36125,7 +36125,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -36163,7 +36163,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -36201,7 +36201,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -36239,7 +36239,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -36277,7 +36277,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -36315,7 +36315,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -36353,7 +36353,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -36391,7 +36391,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -36429,7 +36429,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -36467,7 +36467,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -36505,7 +36505,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -36581,7 +36581,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -36619,7 +36619,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -36657,7 +36657,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -36695,7 +36695,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -36733,7 +36733,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -36771,7 +36771,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -36847,7 +36847,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -36885,7 +36885,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -36923,7 +36923,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -36961,7 +36961,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -36999,7 +36999,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -37037,7 +37037,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -37075,7 +37075,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -37113,7 +37113,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -37151,7 +37151,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -37189,7 +37189,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -37227,7 +37227,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -37265,7 +37265,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -37303,7 +37303,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -37341,7 +37341,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -37379,7 +37379,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -37417,7 +37417,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -37455,7 +37455,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -37493,7 +37493,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -37531,7 +37531,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -37569,7 +37569,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -37607,7 +37607,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -37645,7 +37645,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -37721,7 +37721,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -37759,7 +37759,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -37797,7 +37797,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -37835,7 +37835,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -37873,7 +37873,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -37911,7 +37911,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -37949,7 +37949,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -37987,7 +37987,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -38025,7 +38025,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -38063,7 +38063,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -38101,7 +38101,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -38139,7 +38139,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -38177,7 +38177,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -38215,7 +38215,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -38253,7 +38253,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -38291,7 +38291,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -38329,7 +38329,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -38367,7 +38367,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -38405,7 +38405,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -38443,7 +38443,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H480" s="4" t="inlineStr"/>
@@ -38481,7 +38481,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H481" s="4" t="inlineStr"/>
@@ -38519,7 +38519,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H482" s="4" t="inlineStr"/>
@@ -38557,7 +38557,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H483" s="4" t="inlineStr"/>
@@ -38595,7 +38595,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H484" s="4" t="inlineStr"/>
@@ -38633,7 +38633,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H485" s="4" t="inlineStr"/>
@@ -38671,7 +38671,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H486" s="4" t="inlineStr"/>
@@ -38709,7 +38709,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H487" s="4" t="inlineStr"/>
@@ -38747,7 +38747,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H488" s="4" t="inlineStr"/>
@@ -38785,7 +38785,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H489" s="4" t="inlineStr"/>
@@ -38823,7 +38823,7 @@
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H490" s="4" t="inlineStr"/>
@@ -38861,7 +38861,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H491" s="4" t="inlineStr"/>
@@ -38899,7 +38899,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H492" s="4" t="inlineStr"/>
@@ -38937,7 +38937,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H493" s="4" t="inlineStr"/>
@@ -38975,7 +38975,7 @@
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H494" s="4" t="inlineStr"/>
@@ -39013,7 +39013,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H495" s="4" t="inlineStr"/>
@@ -39051,7 +39051,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H496" s="4" t="inlineStr"/>
@@ -39089,7 +39089,7 @@
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H497" s="4" t="inlineStr"/>
@@ -39127,7 +39127,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H498" s="4" t="inlineStr"/>
@@ -39165,7 +39165,7 @@
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H499" s="4" t="inlineStr"/>
@@ -39203,7 +39203,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H500" s="4" t="inlineStr"/>
@@ -39241,7 +39241,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H501" s="4" t="inlineStr"/>
@@ -39279,7 +39279,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H502" s="4" t="inlineStr"/>
@@ -39317,7 +39317,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H503" s="4" t="inlineStr"/>
@@ -39355,7 +39355,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H504" s="4" t="inlineStr"/>
@@ -39393,7 +39393,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H505" s="4" t="inlineStr"/>
@@ -39431,7 +39431,7 @@
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H506" s="4" t="inlineStr"/>
@@ -39469,7 +39469,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H507" s="4" t="inlineStr"/>
@@ -39507,7 +39507,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H508" s="4" t="inlineStr"/>
@@ -39545,7 +39545,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H509" s="4" t="inlineStr"/>
@@ -39583,7 +39583,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H510" s="4" t="inlineStr"/>
@@ -39621,7 +39621,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H511" s="4" t="inlineStr"/>
@@ -39659,7 +39659,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H512" s="4" t="inlineStr"/>
@@ -39697,7 +39697,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H513" s="4" t="inlineStr"/>
@@ -39735,7 +39735,7 @@
       </c>
       <c r="G514" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H514" s="4" t="inlineStr"/>
@@ -39773,7 +39773,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H515" s="4" t="inlineStr"/>
@@ -39811,7 +39811,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H516" s="4" t="inlineStr"/>
@@ -39849,7 +39849,7 @@
       </c>
       <c r="G517" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H517" s="4" t="inlineStr"/>
@@ -39887,7 +39887,7 @@
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H518" s="4" t="inlineStr"/>
@@ -39925,7 +39925,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H519" s="4" t="inlineStr"/>
@@ -39963,7 +39963,7 @@
       </c>
       <c r="G520" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H520" s="4" t="inlineStr"/>
@@ -40001,7 +40001,7 @@
       </c>
       <c r="G521" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:22</t>
+          <t>2026-06-24 06:47:33</t>
         </is>
       </c>
       <c r="H521" s="4" t="inlineStr"/>
@@ -40272,7 +40272,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>2026-06-24 06:11:24</t>
+          <t>2026-06-24 06:47:35</t>
         </is>
       </c>
     </row>

--- a/reports/latest/android/Excel/Automation_Test_Report.xlsx
+++ b/reports/latest/android/Excel/Automation_Test_Report.xlsx
@@ -594,12 +594,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>24.02</t>
+          <t>31.09</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:43:35</t>
+          <t>2026-06-24 07:25:59</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -632,12 +632,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>33.40</t>
+          <t>38.40</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:44:08</t>
+          <t>2026-06-24 07:26:37</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -670,12 +670,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>31.97</t>
+          <t>44.47</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:44:40</t>
+          <t>2026-06-24 07:27:22</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -708,12 +708,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>33.52</t>
+          <t>37.31</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:45:14</t>
+          <t>2026-06-24 07:27:59</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -746,12 +746,12 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>36.91</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:45:46</t>
+          <t>2026-06-24 07:28:36</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -784,12 +784,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:46:18</t>
+          <t>2026-06-24 07:29:11</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -822,12 +822,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>43.29</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:46:57</t>
+          <t>2026-06-24 07:29:54</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -860,12 +860,12 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>38.88</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -898,12 +898,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -941,7 +941,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -979,7 +979,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -6223,7 +6223,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -7477,7 +7477,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -7553,7 +7553,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -7667,7 +7667,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -8427,7 +8427,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -8465,7 +8465,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -9073,7 +9073,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -9567,7 +9567,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -9795,7 +9795,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -9947,7 +9947,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -9985,7 +9985,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -10023,7 +10023,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -10061,7 +10061,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -10099,7 +10099,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -10213,7 +10213,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -10251,7 +10251,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -10441,7 +10441,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -10517,7 +10517,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -10555,7 +10555,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -10593,7 +10593,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -10669,7 +10669,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -10783,7 +10783,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -10897,7 +10897,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -10935,7 +10935,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -11011,7 +11011,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -11277,7 +11277,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -11353,7 +11353,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -11505,7 +11505,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -11543,7 +11543,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -11657,7 +11657,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -11733,7 +11733,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -11847,7 +11847,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -11923,7 +11923,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -12037,7 +12037,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -12075,7 +12075,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -12189,7 +12189,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -12227,7 +12227,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -12265,7 +12265,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -12303,7 +12303,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -12341,7 +12341,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -12531,7 +12531,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -12607,7 +12607,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -12645,7 +12645,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -12721,7 +12721,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -12911,7 +12911,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -12949,7 +12949,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -12987,7 +12987,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -13063,7 +13063,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -13101,7 +13101,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -13291,7 +13291,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -13443,7 +13443,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -13481,7 +13481,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -13519,7 +13519,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -13595,7 +13595,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -13709,7 +13709,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -13747,7 +13747,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -13785,7 +13785,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -13823,7 +13823,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -13861,7 +13861,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -14089,7 +14089,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -14127,7 +14127,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -14165,7 +14165,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -14203,7 +14203,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -14241,7 +14241,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -14431,7 +14431,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -14469,7 +14469,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -14545,7 +14545,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -14659,7 +14659,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -14697,7 +14697,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -14735,7 +14735,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -14773,7 +14773,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -14811,7 +14811,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -14849,7 +14849,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -14887,7 +14887,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -14925,7 +14925,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -14963,7 +14963,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -15001,7 +15001,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -15039,7 +15039,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -15153,7 +15153,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -15191,7 +15191,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -15267,7 +15267,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -15305,7 +15305,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -15381,7 +15381,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -15419,7 +15419,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -15457,7 +15457,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -15495,7 +15495,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -15571,7 +15571,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -15609,7 +15609,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -15685,7 +15685,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -15723,7 +15723,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -15799,7 +15799,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -15837,7 +15837,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -15875,7 +15875,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -15951,7 +15951,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -15989,7 +15989,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -16065,7 +16065,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -16103,7 +16103,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -16141,7 +16141,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -16179,7 +16179,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -16217,7 +16217,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -16255,7 +16255,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -16293,7 +16293,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -16407,7 +16407,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -16483,7 +16483,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -16521,7 +16521,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -16597,7 +16597,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -16673,7 +16673,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -16711,7 +16711,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -16749,7 +16749,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -16825,7 +16825,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -16863,7 +16863,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -16939,7 +16939,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -16977,7 +16977,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -17053,7 +17053,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -17091,7 +17091,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -17129,7 +17129,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -17167,7 +17167,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -17205,7 +17205,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -17243,7 +17243,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -17319,7 +17319,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -17357,7 +17357,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -17433,7 +17433,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -17471,7 +17471,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -17509,7 +17509,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -17547,7 +17547,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -17585,7 +17585,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -17737,7 +17737,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -17775,7 +17775,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -17813,7 +17813,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -17851,7 +17851,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -17965,7 +17965,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -18003,7 +18003,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -18079,7 +18079,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -18117,7 +18117,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -18155,7 +18155,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -18231,7 +18231,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -18269,7 +18269,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -18307,7 +18307,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -18345,7 +18345,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -18383,7 +18383,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -18421,7 +18421,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -18459,7 +18459,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -18497,7 +18497,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -18535,7 +18535,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -18573,7 +18573,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -18611,7 +18611,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -18649,7 +18649,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -18687,7 +18687,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H480" s="4" t="inlineStr"/>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H481" s="4" t="inlineStr"/>
@@ -18763,7 +18763,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H482" s="4" t="inlineStr"/>
@@ -18801,7 +18801,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H483" s="4" t="inlineStr"/>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H484" s="4" t="inlineStr"/>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H485" s="4" t="inlineStr"/>
@@ -18915,7 +18915,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H486" s="4" t="inlineStr"/>
@@ -18953,7 +18953,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H487" s="4" t="inlineStr"/>
@@ -18991,7 +18991,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H488" s="4" t="inlineStr"/>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H489" s="4" t="inlineStr"/>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H490" s="4" t="inlineStr"/>
@@ -19105,7 +19105,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H491" s="4" t="inlineStr"/>
@@ -19143,7 +19143,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H492" s="4" t="inlineStr"/>
@@ -19181,7 +19181,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H493" s="4" t="inlineStr"/>
@@ -19219,7 +19219,7 @@
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H494" s="4" t="inlineStr"/>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H495" s="4" t="inlineStr"/>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H496" s="4" t="inlineStr"/>
@@ -19333,7 +19333,7 @@
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H497" s="4" t="inlineStr"/>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H498" s="4" t="inlineStr"/>
@@ -19409,7 +19409,7 @@
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H499" s="4" t="inlineStr"/>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H500" s="4" t="inlineStr"/>
@@ -19485,7 +19485,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H501" s="4" t="inlineStr"/>
@@ -19523,7 +19523,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H502" s="4" t="inlineStr"/>
@@ -19561,7 +19561,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H503" s="4" t="inlineStr"/>
@@ -19599,7 +19599,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H504" s="4" t="inlineStr"/>
@@ -19637,7 +19637,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H505" s="4" t="inlineStr"/>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H506" s="4" t="inlineStr"/>
@@ -19713,7 +19713,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H507" s="4" t="inlineStr"/>
@@ -19751,7 +19751,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H508" s="4" t="inlineStr"/>
@@ -19789,7 +19789,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H509" s="4" t="inlineStr"/>
@@ -19827,7 +19827,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H510" s="4" t="inlineStr"/>
@@ -19865,7 +19865,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H511" s="4" t="inlineStr"/>
@@ -19903,7 +19903,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H512" s="4" t="inlineStr"/>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H513" s="4" t="inlineStr"/>
@@ -19979,7 +19979,7 @@
       </c>
       <c r="G514" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H514" s="4" t="inlineStr"/>
@@ -20017,7 +20017,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H515" s="4" t="inlineStr"/>
@@ -20055,7 +20055,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H516" s="4" t="inlineStr"/>
@@ -20093,7 +20093,7 @@
       </c>
       <c r="G517" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H517" s="4" t="inlineStr"/>
@@ -20131,7 +20131,7 @@
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H518" s="4" t="inlineStr"/>
@@ -20169,7 +20169,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H519" s="4" t="inlineStr"/>
@@ -20207,7 +20207,7 @@
       </c>
       <c r="G520" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H520" s="4" t="inlineStr"/>
@@ -20245,7 +20245,7 @@
       </c>
       <c r="G521" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H521" s="4" t="inlineStr"/>
@@ -20350,12 +20350,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>24.02</t>
+          <t>31.09</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:43:35</t>
+          <t>2026-06-24 07:25:59</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -20388,12 +20388,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>33.40</t>
+          <t>38.40</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:44:08</t>
+          <t>2026-06-24 07:26:37</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -20426,12 +20426,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>31.97</t>
+          <t>44.47</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:44:40</t>
+          <t>2026-06-24 07:27:22</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -20464,12 +20464,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>33.52</t>
+          <t>37.31</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:45:14</t>
+          <t>2026-06-24 07:27:59</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -20502,12 +20502,12 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>36.91</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:45:46</t>
+          <t>2026-06-24 07:28:36</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
@@ -20540,12 +20540,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:46:18</t>
+          <t>2026-06-24 07:29:11</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -20578,12 +20578,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>43.29</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:46:57</t>
+          <t>2026-06-24 07:29:54</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -20616,12 +20616,12 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>38.88</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -20654,12 +20654,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -20697,7 +20697,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -20735,7 +20735,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -20773,7 +20773,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -20811,7 +20811,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -20849,7 +20849,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -20887,7 +20887,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -20925,7 +20925,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -20963,7 +20963,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -21001,7 +21001,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -21039,7 +21039,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -21115,7 +21115,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -21153,7 +21153,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -21191,7 +21191,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -21229,7 +21229,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -21267,7 +21267,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -21305,7 +21305,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -21343,7 +21343,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -21419,7 +21419,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -21495,7 +21495,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
@@ -21533,7 +21533,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -21571,7 +21571,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -21647,7 +21647,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
@@ -21685,7 +21685,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -21723,7 +21723,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
@@ -21761,7 +21761,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
@@ -21875,7 +21875,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -21913,7 +21913,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -21951,7 +21951,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -21989,7 +21989,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
@@ -22027,7 +22027,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
@@ -22065,7 +22065,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
@@ -22103,7 +22103,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -22141,7 +22141,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -22179,7 +22179,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
@@ -22217,7 +22217,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -22255,7 +22255,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -22293,7 +22293,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -22331,7 +22331,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
@@ -22369,7 +22369,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -22407,7 +22407,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -22445,7 +22445,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -22521,7 +22521,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -22559,7 +22559,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -22597,7 +22597,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -22635,7 +22635,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -22711,7 +22711,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
@@ -22749,7 +22749,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -22787,7 +22787,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -22825,7 +22825,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
@@ -22901,7 +22901,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -22939,7 +22939,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
@@ -22977,7 +22977,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -23015,7 +23015,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
@@ -23053,7 +23053,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -23091,7 +23091,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
@@ -23167,7 +23167,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
@@ -23205,7 +23205,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
@@ -23243,7 +23243,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -23281,7 +23281,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
@@ -23319,7 +23319,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -23357,7 +23357,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
@@ -23395,7 +23395,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
@@ -23433,7 +23433,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
@@ -23509,7 +23509,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -23547,7 +23547,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
@@ -23585,7 +23585,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -23623,7 +23623,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -23661,7 +23661,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -23699,7 +23699,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
@@ -23737,7 +23737,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -23775,7 +23775,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -23813,7 +23813,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
@@ -23851,7 +23851,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -23889,7 +23889,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
@@ -23927,7 +23927,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -23965,7 +23965,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
@@ -24003,7 +24003,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -24041,7 +24041,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -24079,7 +24079,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -24117,7 +24117,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -24193,7 +24193,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
@@ -24231,7 +24231,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
@@ -24307,7 +24307,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
@@ -24345,7 +24345,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
@@ -24383,7 +24383,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -24421,7 +24421,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -24459,7 +24459,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
@@ -24497,7 +24497,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
@@ -24535,7 +24535,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
@@ -24573,7 +24573,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
@@ -24611,7 +24611,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
@@ -24649,7 +24649,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -24687,7 +24687,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -24725,7 +24725,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
@@ -24763,7 +24763,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -24801,7 +24801,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
@@ -24839,7 +24839,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -24877,7 +24877,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
@@ -24915,7 +24915,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
@@ -24953,7 +24953,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
@@ -24991,7 +24991,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -25029,7 +25029,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
@@ -25067,7 +25067,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -25105,7 +25105,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
@@ -25143,7 +25143,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
@@ -25219,7 +25219,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
@@ -25257,7 +25257,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
@@ -25295,7 +25295,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
@@ -25333,7 +25333,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -25371,7 +25371,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -25409,7 +25409,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
@@ -25447,7 +25447,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
@@ -25485,7 +25485,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
@@ -25523,7 +25523,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -25561,7 +25561,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
@@ -25599,7 +25599,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
@@ -25637,7 +25637,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
@@ -25675,7 +25675,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
@@ -25713,7 +25713,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -25751,7 +25751,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -25789,7 +25789,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
@@ -25827,7 +25827,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
@@ -25865,7 +25865,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
@@ -25903,7 +25903,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
@@ -25941,7 +25941,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
@@ -25979,7 +25979,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -26017,7 +26017,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
@@ -26055,7 +26055,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
@@ -26093,7 +26093,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
@@ -26169,7 +26169,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
@@ -26207,7 +26207,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
@@ -26245,7 +26245,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
@@ -26359,7 +26359,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
@@ -26397,7 +26397,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
@@ -26435,7 +26435,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
@@ -26473,7 +26473,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
@@ -26511,7 +26511,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -26549,7 +26549,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
@@ -26587,7 +26587,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
@@ -26625,7 +26625,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
@@ -26663,7 +26663,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
@@ -26701,7 +26701,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
@@ -26739,7 +26739,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
@@ -26815,7 +26815,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
@@ -26853,7 +26853,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
@@ -26891,7 +26891,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
@@ -26929,7 +26929,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
@@ -26967,7 +26967,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
@@ -27005,7 +27005,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
@@ -27043,7 +27043,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
@@ -27081,7 +27081,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
@@ -27119,7 +27119,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
@@ -27157,7 +27157,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -27233,7 +27233,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
@@ -27271,7 +27271,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
@@ -27309,7 +27309,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
@@ -27347,7 +27347,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
@@ -27385,7 +27385,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
@@ -27423,7 +27423,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
@@ -27461,7 +27461,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
@@ -27499,7 +27499,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
@@ -27537,7 +27537,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
@@ -27575,7 +27575,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
@@ -27613,7 +27613,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
@@ -27651,7 +27651,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -27689,7 +27689,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
@@ -27727,7 +27727,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
@@ -27765,7 +27765,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
@@ -27803,7 +27803,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
@@ -27841,7 +27841,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
@@ -27879,7 +27879,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
@@ -27917,7 +27917,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
@@ -27955,7 +27955,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
@@ -27993,7 +27993,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
@@ -28031,7 +28031,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr"/>
@@ -28107,7 +28107,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr"/>
@@ -28145,7 +28145,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr"/>
@@ -28183,7 +28183,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr"/>
@@ -28221,7 +28221,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr"/>
@@ -28259,7 +28259,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr"/>
@@ -28297,7 +28297,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr"/>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr"/>
@@ -28373,7 +28373,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -28411,7 +28411,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -28449,7 +28449,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr"/>
@@ -28487,7 +28487,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr"/>
@@ -28525,7 +28525,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr"/>
@@ -28563,7 +28563,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -28601,7 +28601,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr"/>
@@ -28639,7 +28639,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr"/>
@@ -28677,7 +28677,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
@@ -28715,7 +28715,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -28753,7 +28753,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr"/>
@@ -28791,7 +28791,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr"/>
@@ -28829,7 +28829,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -28867,7 +28867,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr"/>
@@ -28905,7 +28905,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr"/>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr"/>
@@ -28981,7 +28981,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr"/>
@@ -29019,7 +29019,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr"/>
@@ -29057,7 +29057,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr"/>
@@ -29095,7 +29095,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr"/>
@@ -29133,7 +29133,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr"/>
@@ -29171,7 +29171,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr"/>
@@ -29209,7 +29209,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -29247,7 +29247,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr"/>
@@ -29285,7 +29285,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr"/>
@@ -29323,7 +29323,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr"/>
@@ -29361,7 +29361,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -29399,7 +29399,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr"/>
@@ -29437,7 +29437,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr"/>
@@ -29475,7 +29475,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -29513,7 +29513,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr"/>
@@ -29551,7 +29551,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr"/>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr"/>
@@ -29627,7 +29627,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr"/>
@@ -29665,7 +29665,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr"/>
@@ -29703,7 +29703,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -29741,7 +29741,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -29779,7 +29779,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr"/>
@@ -29855,7 +29855,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -29893,7 +29893,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>
@@ -29931,7 +29931,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr"/>
@@ -29969,7 +29969,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr"/>
@@ -30007,7 +30007,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -30045,7 +30045,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr"/>
@@ -30083,7 +30083,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
@@ -30121,7 +30121,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
@@ -30159,7 +30159,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr"/>
@@ -30197,7 +30197,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr"/>
@@ -30235,7 +30235,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr"/>
@@ -30273,7 +30273,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr"/>
@@ -30311,7 +30311,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr"/>
@@ -30349,7 +30349,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr"/>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr"/>
@@ -30425,7 +30425,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr"/>
@@ -30463,7 +30463,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr"/>
@@ -30501,7 +30501,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr"/>
@@ -30539,7 +30539,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr"/>
@@ -30577,7 +30577,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr"/>
@@ -30615,7 +30615,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr"/>
@@ -30653,7 +30653,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr"/>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr"/>
@@ -30729,7 +30729,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr"/>
@@ -30767,7 +30767,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr"/>
@@ -30805,7 +30805,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr"/>
@@ -30843,7 +30843,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr"/>
@@ -30881,7 +30881,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr"/>
@@ -30919,7 +30919,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr"/>
@@ -30957,7 +30957,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr"/>
@@ -30995,7 +30995,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr"/>
@@ -31033,7 +31033,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H285" s="4" t="inlineStr"/>
@@ -31071,7 +31071,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr"/>
@@ -31109,7 +31109,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr"/>
@@ -31147,7 +31147,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H288" s="4" t="inlineStr"/>
@@ -31185,7 +31185,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr"/>
@@ -31223,7 +31223,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr"/>
@@ -31261,7 +31261,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr"/>
@@ -31299,7 +31299,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H292" s="4" t="inlineStr"/>
@@ -31337,7 +31337,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -31375,7 +31375,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -31413,7 +31413,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr"/>
@@ -31451,7 +31451,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -31489,7 +31489,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr"/>
@@ -31527,7 +31527,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr"/>
@@ -31565,7 +31565,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr"/>
@@ -31603,7 +31603,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr"/>
@@ -31641,7 +31641,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr"/>
@@ -31679,7 +31679,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
@@ -31717,7 +31717,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr"/>
@@ -31755,7 +31755,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr"/>
@@ -31793,7 +31793,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr"/>
@@ -31831,7 +31831,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr"/>
@@ -31869,7 +31869,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr"/>
@@ -31907,7 +31907,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr"/>
@@ -31945,7 +31945,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr"/>
@@ -31983,7 +31983,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr"/>
@@ -32021,7 +32021,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr"/>
@@ -32059,7 +32059,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr"/>
@@ -32097,7 +32097,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr"/>
@@ -32135,7 +32135,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr"/>
@@ -32173,7 +32173,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr"/>
@@ -32211,7 +32211,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr"/>
@@ -32249,7 +32249,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr"/>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr"/>
@@ -32325,7 +32325,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr"/>
@@ -32363,7 +32363,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr"/>
@@ -32401,7 +32401,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr"/>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -32477,7 +32477,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -32515,7 +32515,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr"/>
@@ -32553,7 +32553,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr"/>
@@ -32591,7 +32591,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr"/>
@@ -32629,7 +32629,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr"/>
@@ -32667,7 +32667,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr"/>
@@ -32705,7 +32705,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr"/>
@@ -32743,7 +32743,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr"/>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H331" s="4" t="inlineStr"/>
@@ -32819,7 +32819,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr"/>
@@ -32857,7 +32857,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H333" s="4" t="inlineStr"/>
@@ -32895,7 +32895,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H334" s="4" t="inlineStr"/>
@@ -32933,7 +32933,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H335" s="4" t="inlineStr"/>
@@ -32971,7 +32971,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H336" s="4" t="inlineStr"/>
@@ -33009,7 +33009,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H337" s="4" t="inlineStr"/>
@@ -33047,7 +33047,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H338" s="4" t="inlineStr"/>
@@ -33085,7 +33085,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H339" s="4" t="inlineStr"/>
@@ -33123,7 +33123,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H340" s="4" t="inlineStr"/>
@@ -33161,7 +33161,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H341" s="4" t="inlineStr"/>
@@ -33199,7 +33199,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H342" s="4" t="inlineStr"/>
@@ -33237,7 +33237,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H343" s="4" t="inlineStr"/>
@@ -33275,7 +33275,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H345" s="4" t="inlineStr"/>
@@ -33351,7 +33351,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H346" s="4" t="inlineStr"/>
@@ -33389,7 +33389,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H347" s="4" t="inlineStr"/>
@@ -33427,7 +33427,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H348" s="4" t="inlineStr"/>
@@ -33465,7 +33465,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H349" s="4" t="inlineStr"/>
@@ -33503,7 +33503,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H350" s="4" t="inlineStr"/>
@@ -33541,7 +33541,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H351" s="4" t="inlineStr"/>
@@ -33579,7 +33579,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H352" s="4" t="inlineStr"/>
@@ -33617,7 +33617,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H353" s="4" t="inlineStr"/>
@@ -33655,7 +33655,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H354" s="4" t="inlineStr"/>
@@ -33693,7 +33693,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H355" s="4" t="inlineStr"/>
@@ -33731,7 +33731,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H356" s="4" t="inlineStr"/>
@@ -33769,7 +33769,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr"/>
@@ -33807,7 +33807,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H358" s="4" t="inlineStr"/>
@@ -33845,7 +33845,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H359" s="4" t="inlineStr"/>
@@ -33883,7 +33883,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H360" s="4" t="inlineStr"/>
@@ -33921,7 +33921,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H361" s="4" t="inlineStr"/>
@@ -33959,7 +33959,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H362" s="4" t="inlineStr"/>
@@ -33997,7 +33997,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H363" s="4" t="inlineStr"/>
@@ -34035,7 +34035,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H364" s="4" t="inlineStr"/>
@@ -34073,7 +34073,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H365" s="4" t="inlineStr"/>
@@ -34111,7 +34111,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H366" s="4" t="inlineStr"/>
@@ -34149,7 +34149,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H367" s="4" t="inlineStr"/>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H368" s="4" t="inlineStr"/>
@@ -34225,7 +34225,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H369" s="4" t="inlineStr"/>
@@ -34263,7 +34263,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H370" s="4" t="inlineStr"/>
@@ -34301,7 +34301,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H371" s="4" t="inlineStr"/>
@@ -34339,7 +34339,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H372" s="4" t="inlineStr"/>
@@ -34377,7 +34377,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H373" s="4" t="inlineStr"/>
@@ -34415,7 +34415,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H374" s="4" t="inlineStr"/>
@@ -34453,7 +34453,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H375" s="4" t="inlineStr"/>
@@ -34491,7 +34491,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H376" s="4" t="inlineStr"/>
@@ -34529,7 +34529,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H377" s="4" t="inlineStr"/>
@@ -34567,7 +34567,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H378" s="4" t="inlineStr"/>
@@ -34605,7 +34605,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H379" s="4" t="inlineStr"/>
@@ -34643,7 +34643,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H380" s="4" t="inlineStr"/>
@@ -34681,7 +34681,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H381" s="4" t="inlineStr"/>
@@ -34719,7 +34719,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H382" s="4" t="inlineStr"/>
@@ -34757,7 +34757,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H383" s="4" t="inlineStr"/>
@@ -34795,7 +34795,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H384" s="4" t="inlineStr"/>
@@ -34833,7 +34833,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H385" s="4" t="inlineStr"/>
@@ -34871,7 +34871,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H386" s="4" t="inlineStr"/>
@@ -34909,7 +34909,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H387" s="4" t="inlineStr"/>
@@ -34947,7 +34947,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H388" s="4" t="inlineStr"/>
@@ -34985,7 +34985,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H389" s="4" t="inlineStr"/>
@@ -35023,7 +35023,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H390" s="4" t="inlineStr"/>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H391" s="4" t="inlineStr"/>
@@ -35099,7 +35099,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H392" s="4" t="inlineStr"/>
@@ -35137,7 +35137,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H393" s="4" t="inlineStr"/>
@@ -35175,7 +35175,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H394" s="4" t="inlineStr"/>
@@ -35213,7 +35213,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H395" s="4" t="inlineStr"/>
@@ -35251,7 +35251,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H396" s="4" t="inlineStr"/>
@@ -35289,7 +35289,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H397" s="4" t="inlineStr"/>
@@ -35327,7 +35327,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H398" s="4" t="inlineStr"/>
@@ -35365,7 +35365,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H399" s="4" t="inlineStr"/>
@@ -35403,7 +35403,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H400" s="4" t="inlineStr"/>
@@ -35441,7 +35441,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H401" s="4" t="inlineStr"/>
@@ -35479,7 +35479,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H402" s="4" t="inlineStr"/>
@@ -35517,7 +35517,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H403" s="4" t="inlineStr"/>
@@ -35555,7 +35555,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H404" s="4" t="inlineStr"/>
@@ -35593,7 +35593,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H405" s="4" t="inlineStr"/>
@@ -35631,7 +35631,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H406" s="4" t="inlineStr"/>
@@ -35669,7 +35669,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H407" s="4" t="inlineStr"/>
@@ -35707,7 +35707,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H408" s="4" t="inlineStr"/>
@@ -35745,7 +35745,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H409" s="4" t="inlineStr"/>
@@ -35783,7 +35783,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H410" s="4" t="inlineStr"/>
@@ -35821,7 +35821,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr"/>
@@ -35859,7 +35859,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H412" s="4" t="inlineStr"/>
@@ -35897,7 +35897,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H413" s="4" t="inlineStr"/>
@@ -35935,7 +35935,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H414" s="4" t="inlineStr"/>
@@ -35973,7 +35973,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H415" s="4" t="inlineStr"/>
@@ -36011,7 +36011,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H416" s="4" t="inlineStr"/>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H417" s="4" t="inlineStr"/>
@@ -36087,7 +36087,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H418" s="4" t="inlineStr"/>
@@ -36125,7 +36125,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H419" s="4" t="inlineStr"/>
@@ -36163,7 +36163,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H420" s="4" t="inlineStr"/>
@@ -36201,7 +36201,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H421" s="4" t="inlineStr"/>
@@ -36239,7 +36239,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H422" s="4" t="inlineStr"/>
@@ -36277,7 +36277,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H423" s="4" t="inlineStr"/>
@@ -36315,7 +36315,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H424" s="4" t="inlineStr"/>
@@ -36353,7 +36353,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H425" s="4" t="inlineStr"/>
@@ -36391,7 +36391,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H426" s="4" t="inlineStr"/>
@@ -36429,7 +36429,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H427" s="4" t="inlineStr"/>
@@ -36467,7 +36467,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H428" s="4" t="inlineStr"/>
@@ -36505,7 +36505,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H429" s="4" t="inlineStr"/>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H430" s="4" t="inlineStr"/>
@@ -36581,7 +36581,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H431" s="4" t="inlineStr"/>
@@ -36619,7 +36619,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -36657,7 +36657,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>
@@ -36695,7 +36695,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H434" s="4" t="inlineStr"/>
@@ -36733,7 +36733,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H435" s="4" t="inlineStr"/>
@@ -36771,7 +36771,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H436" s="4" t="inlineStr"/>
@@ -36809,7 +36809,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H437" s="4" t="inlineStr"/>
@@ -36847,7 +36847,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H438" s="4" t="inlineStr"/>
@@ -36885,7 +36885,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H439" s="4" t="inlineStr"/>
@@ -36923,7 +36923,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H440" s="4" t="inlineStr"/>
@@ -36961,7 +36961,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H441" s="4" t="inlineStr"/>
@@ -36999,7 +36999,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H442" s="4" t="inlineStr"/>
@@ -37037,7 +37037,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H443" s="4" t="inlineStr"/>
@@ -37075,7 +37075,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H444" s="4" t="inlineStr"/>
@@ -37113,7 +37113,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H445" s="4" t="inlineStr"/>
@@ -37151,7 +37151,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H446" s="4" t="inlineStr"/>
@@ -37189,7 +37189,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H447" s="4" t="inlineStr"/>
@@ -37227,7 +37227,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H448" s="4" t="inlineStr"/>
@@ -37265,7 +37265,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H449" s="4" t="inlineStr"/>
@@ -37303,7 +37303,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H450" s="4" t="inlineStr"/>
@@ -37341,7 +37341,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H451" s="4" t="inlineStr"/>
@@ -37379,7 +37379,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H452" s="4" t="inlineStr"/>
@@ -37417,7 +37417,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H453" s="4" t="inlineStr"/>
@@ -37455,7 +37455,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H454" s="4" t="inlineStr"/>
@@ -37493,7 +37493,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H455" s="4" t="inlineStr"/>
@@ -37531,7 +37531,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H456" s="4" t="inlineStr"/>
@@ -37569,7 +37569,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H457" s="4" t="inlineStr"/>
@@ -37607,7 +37607,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H458" s="4" t="inlineStr"/>
@@ -37645,7 +37645,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H459" s="4" t="inlineStr"/>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H460" s="4" t="inlineStr"/>
@@ -37721,7 +37721,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H461" s="4" t="inlineStr"/>
@@ -37759,7 +37759,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H462" s="4" t="inlineStr"/>
@@ -37797,7 +37797,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H463" s="4" t="inlineStr"/>
@@ -37835,7 +37835,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H464" s="4" t="inlineStr"/>
@@ -37873,7 +37873,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H465" s="4" t="inlineStr"/>
@@ -37911,7 +37911,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H466" s="4" t="inlineStr"/>
@@ -37949,7 +37949,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H467" s="4" t="inlineStr"/>
@@ -37987,7 +37987,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H468" s="4" t="inlineStr"/>
@@ -38025,7 +38025,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H469" s="4" t="inlineStr"/>
@@ -38063,7 +38063,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H470" s="4" t="inlineStr"/>
@@ -38101,7 +38101,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H471" s="4" t="inlineStr"/>
@@ -38139,7 +38139,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H472" s="4" t="inlineStr"/>
@@ -38177,7 +38177,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H473" s="4" t="inlineStr"/>
@@ -38215,7 +38215,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H474" s="4" t="inlineStr"/>
@@ -38253,7 +38253,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H475" s="4" t="inlineStr"/>
@@ -38291,7 +38291,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H476" s="4" t="inlineStr"/>
@@ -38329,7 +38329,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H477" s="4" t="inlineStr"/>
@@ -38367,7 +38367,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H478" s="4" t="inlineStr"/>
@@ -38405,7 +38405,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H479" s="4" t="inlineStr"/>
@@ -38443,7 +38443,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H480" s="4" t="inlineStr"/>
@@ -38481,7 +38481,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H481" s="4" t="inlineStr"/>
@@ -38519,7 +38519,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H482" s="4" t="inlineStr"/>
@@ -38557,7 +38557,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H483" s="4" t="inlineStr"/>
@@ -38595,7 +38595,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H484" s="4" t="inlineStr"/>
@@ -38633,7 +38633,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H485" s="4" t="inlineStr"/>
@@ -38671,7 +38671,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H486" s="4" t="inlineStr"/>
@@ -38709,7 +38709,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H487" s="4" t="inlineStr"/>
@@ -38747,7 +38747,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H488" s="4" t="inlineStr"/>
@@ -38785,7 +38785,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H489" s="4" t="inlineStr"/>
@@ -38823,7 +38823,7 @@
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H490" s="4" t="inlineStr"/>
@@ -38861,7 +38861,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H491" s="4" t="inlineStr"/>
@@ -38899,7 +38899,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H492" s="4" t="inlineStr"/>
@@ -38937,7 +38937,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H493" s="4" t="inlineStr"/>
@@ -38975,7 +38975,7 @@
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H494" s="4" t="inlineStr"/>
@@ -39013,7 +39013,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H495" s="4" t="inlineStr"/>
@@ -39051,7 +39051,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H496" s="4" t="inlineStr"/>
@@ -39089,7 +39089,7 @@
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H497" s="4" t="inlineStr"/>
@@ -39127,7 +39127,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H498" s="4" t="inlineStr"/>
@@ -39165,7 +39165,7 @@
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H499" s="4" t="inlineStr"/>
@@ -39203,7 +39203,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H500" s="4" t="inlineStr"/>
@@ -39241,7 +39241,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H501" s="4" t="inlineStr"/>
@@ -39279,7 +39279,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H502" s="4" t="inlineStr"/>
@@ -39317,7 +39317,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H503" s="4" t="inlineStr"/>
@@ -39355,7 +39355,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H504" s="4" t="inlineStr"/>
@@ -39393,7 +39393,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H505" s="4" t="inlineStr"/>
@@ -39431,7 +39431,7 @@
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H506" s="4" t="inlineStr"/>
@@ -39469,7 +39469,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H507" s="4" t="inlineStr"/>
@@ -39507,7 +39507,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H508" s="4" t="inlineStr"/>
@@ -39545,7 +39545,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H509" s="4" t="inlineStr"/>
@@ -39583,7 +39583,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H510" s="4" t="inlineStr"/>
@@ -39621,7 +39621,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H511" s="4" t="inlineStr"/>
@@ -39659,7 +39659,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H512" s="4" t="inlineStr"/>
@@ -39697,7 +39697,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H513" s="4" t="inlineStr"/>
@@ -39735,7 +39735,7 @@
       </c>
       <c r="G514" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H514" s="4" t="inlineStr"/>
@@ -39773,7 +39773,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H515" s="4" t="inlineStr"/>
@@ -39811,7 +39811,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H516" s="4" t="inlineStr"/>
@@ -39849,7 +39849,7 @@
       </c>
       <c r="G517" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H517" s="4" t="inlineStr"/>
@@ -39887,7 +39887,7 @@
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H518" s="4" t="inlineStr"/>
@@ -39925,7 +39925,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H519" s="4" t="inlineStr"/>
@@ -39963,7 +39963,7 @@
       </c>
       <c r="G520" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H520" s="4" t="inlineStr"/>
@@ -40001,7 +40001,7 @@
       </c>
       <c r="G521" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:33</t>
+          <t>2026-06-24 07:30:33</t>
         </is>
       </c>
       <c r="H521" s="4" t="inlineStr"/>
@@ -40272,7 +40272,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>2026-06-24 06:47:35</t>
+          <t>2026-06-24 07:30:35</t>
         </is>
       </c>
     </row>
